--- a/RC_Catalogo_Questionarios_v1.xlsx
+++ b/RC_Catalogo_Questionarios_v1.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1674" uniqueCount="1249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1829" uniqueCount="1359">
   <si>
     <t xml:space="preserve">RC · Catálogo de Questionários — Ricardina Correia · OPP 8233</t>
   </si>
@@ -1204,13 +1204,16 @@
     <t xml:space="preserve">DIVA-5</t>
   </si>
   <si>
+    <t xml:space="preserve">Paciente, Cônjuge/Parceiro(a), Mãe, Pai, Enc. Educação, Clínico</t>
+  </si>
+  <si>
     <t xml:space="preserve">5 anos+</t>
   </si>
   <si>
-    <t xml:space="preserve">Entrevista diagnóstica para PHDA — adultos, jovens e DI (DSM-5)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Desatenção; Hiperatividade/Impulsividade; Diagnóstico PHDA</t>
+    <t xml:space="preserve">Entrevista diagnóstica semiestruturada para a PHDA segundo o DSM-5 (Kooij &amp; Francken, 2019), nas três versões: DIVA-5 Adultos, Young DIVA-5 (crianças e adolescentes) e DIVA-5 ID (dificuldade intelectual). Os 18 critérios do DSM-5 — 9 de desatenção (A1–A9) e 9 de hiperatividade/impulsividade (H1–H9) — são avaliados em DOIS períodos: o período actual (adultez, Critério A) e a infância dos 5 aos 12 anos (Critério B). APLICAÇÃO A TRÊS INFORMADORES: o próprio (ambas as colunas), o cônjuge ou parceiro(a) (só o período actual) e os pais (só a infância) preenchem em SEPARADO e SEM SE CONSULTAREM, todos com o MESMO código de paciente. BLOQUEIO DURO DE ÂMBITO: cada informador só vê a coluna sobre a qual tem conhecimento direto — a outra não é renderizada e é submetida como não respondida. O próprio responde às duas colunas; o cônjuge ou parceiro(a) apenas ao período actual; mãe, pai, encarregado de educação e outro familiar apenas à infância. Na Young DIVA-5 o mesmo princípio aplica-se às colunas Jovem e Pais/EE. A restrição é estrutural e não uma instrução: com a coluna aberta, um informador bem-intencionado preenche-a a partir de relato em segunda mão, e como o Critério B é condição necessária e a agregação usa a regra «qualquer informador», esse relato entraria exactamente no critério que decide se há ou não apresentação diagnóstica. Custo aceite: um progenitor que convive hoje com a pessoa avaliada tem conhecimento direto do período actual e deixa de o poder registar por esta via. Os papéis Professor e Técnico/Cuidador ficam sem bloqueio, por o seu âmbito depender do caso. O painel agrega as submissões por código e produz uma grelha de convergência de 18 critérios × N informadores, assinalando os critérios em que os informadores divergem. A cotação composta agrega pela regra «qualquer informador» — um critério conta como presente num período se pelo menos um informador o endossou — mantendo sempre visíveis as contagens individuais, porque a divergência entre informadores é informação clínica e não erro de medida (o próprio subestima com frequência a hiperatividade; o parceiro e os pais servem para corroborar). INSTRUMENTO DE CRITÉRIOS, NÃO NORMATIVO: a cotação é contagem de critérios preenchidos face a um limiar (≥5 em cada domínio, ≥6 na Young DIVA-5 abaixo dos 17 anos). Não produz pontuações padronizadas, percentis nem T-scores, e não admite bandas de gravidade. O Critério B é CONDIÇÃO NECESSÁRIA: nenhuma apresentação diagnóstica é devolvida a partir apenas da coluna do período actual. O Critério A tem protecção simétrica: se a coluna do período actual não estiver preenchida, é devolvido INDETERMINADO e nunca «Não preenche critérios» — a submissão dos pais, que só cobre a infância, não pode ser lida como ausência de sintomatologia actual. São devolvidas DUAS LEITURAS EM PARALELO: a regra DSM-5-TR (Critério B ≥ 2, «vários sintomas» antes dos 12 anos) e a regra DIVA-5 formal (Critério B ≥ 5, o mesmo limiar em ambos os períodos). Quando as duas divergem, a sintomatologia de infância situa-se entre os dois limiares e essa divergência é ela própria informação clínica, a explicitar no relatório. A apresentação é SEMPRE PROVISÓRIA: os Critérios C (≥2 contextos), D (interferência) e E (exclusão de outro quadro) não são recolhidos por este formulário e têm de ser estabelecidos em entrevista — nenhuma conclusão diagnóstica pode assentar apenas nesta grelha. O respondente NÃO vê qualquer resultado: o ecrã final não mostra pontuações nem apresentação diagnóstica, e a cópia de segurança em CSV contém apenas as respostas em bruto.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desatenção — período actual / adultez (critérios A1–A9; Critério A, limiar ≥5); Desatenção — infância dos 5 aos 12 anos (critérios A1–A9; Critério B); Hiperatividade/Impulsividade — período actual / adultez (critérios H1–H9; Critério A, limiar ≥5); Hiperatividade/Impulsividade — infância dos 5 aos 12 anos (critérios H1–H9; Critério B); Estado do Critério A (não avaliado · parcialmente avaliado · preenchido · não preenchido), com contagem dos itens efectivamente respondidos na coluna do período actual; Estado do Critério B (mesmas quatro categorias), com contagem dos itens respondidos na coluna da infância — a contagem é o que distingue «sintoma ausente» de «período não avaliado»; Apresentação pela regra DSM-5-TR, Critério B ≥ 2 (combinada · predominantemente desatenta · predominantemente hiperativa/impulsiva · não preenche critérios · indeterminado); Apresentação pela regra DIVA-5 formal, Critério B ≥ 5 (mesmas categorias) — leitura mais exigente, apresentada lado a lado com a anterior; Âmbito atribuído por informador (período actual · infância · ambos), aplicado por bloqueio estrutural das colunas no formulário; Grelha de convergência entre informadores — 18 critérios × N informadores, com marcação dos critérios divergentes; Cotação composta por agregação «qualquer informador», calculada em separado para cada um dos dois períodos</t>
   </si>
   <si>
     <t xml:space="preserve">diva5</t>
@@ -3653,6 +3656,333 @@
   </si>
   <si>
     <t xml:space="preserve">https://correiaricardina-ui.github.io/questionarios/GCSA_Diario_v1.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIAS · SPS — Escalas de Ansiedade Social</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Próprio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14–99 anos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distingue a ansiedade de INTERAÇÃO social (SIAS, 19 itens, amplitude 0–76; itens 8 e 10 invertidos, valor cotado = 4 menos valor bruto) da ansiedade de ESCRUTÍNIO ou desempenho (SPS, 20 itens, amplitude 0–80; nenhum item invertido), em autorrelato numa escala 0–4 (0 = não é nada característico da minha maneira de ser; 4 = extremamente característico). As duas escalas são sempre aplicadas em conjunto e partilham a mesma aba do Sheet. O RESULTADO PRINCIPAL é a média por item de cada escala e o CONTRASTE entre ambas (SPS menos SIAS, amplitude −4 a +4), que documenta a dissociação intraindividual entre os dois eixos; os totais são secundários. A leitura privilegia a média por item por ser independente do número de itens: a SIAS circula em versões de 19 e de 20 itens, com amplitudes diferentes (0–76 e 0–80), pelo que os totais publicados não são directamente comparáveis entre si. SEM normas portuguesas e SEM pontos de corte nacionais. Os marcadores internacionais são indicativos, apresentam dispersão considerável entre estudos (SIAS 34 a 43; SPS 24 a 27), derivam integralmente de amostras ADULTAS e NÃO são interpretáveis em respondentes com menos de 18 anos; abaixo dos 14 anos estas escalas não são o instrumento indicado. Limite de 2 omissos por escala (convenção operacional, cerca de 10 por cento dos itens, sem base empírica publicada): acima do limite a média e o contraste são devolvidos como não interpretáveis, nunca como zero. A atribuição de um padrão de leitura ao contraste é CLÍNICA e não está automatizada. Todo o apuramento é descritivo; a interpretação clínica é da exclusiva responsabilidade do psicólogo responsável pela avaliação.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ansiedade em situações de interação social, SIAS (média por item 0–4; total 0–76) — falar com figuras de autoridade, manter contacto visual, falar de si próprio, conversar com pessoas pouco conhecidas, discordar, interagir em grupo; Ansiedade de escrutínio ou fobia social, SPS (média por item 0–4; total 0–80) — ser observado a escrever, a comer, a beber, a andar na rua, receio de corar, de tremer, de perder o controlo, de atrair as atenções, falar à frente de outros; Contraste entre as médias por item (SPS menos SIAS, −4 a +4) — saída primária do instrumento, documenta a dissociação entre os dois eixos; Estado do protocolo por escala (completo; omissos dentro do limite de 2; omissos acima do limite, não interpretável); Posição descritiva face aos marcadores internacionais — SIAS 34 (Brown et al., 1997) e 43 (uso corrente na literatura); SPS 24 (Heimberg et al., 1992) e 27 (Peters, 2000); Grelha de leitura do contraste — escrutínio circunscrito; ansiedade social generalizada; ansiedade não organizada no eixo social; padrão atípico a reavaliar — leitura clínica, NÃO automatizada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sias_sps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q_sias_sps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://correiaricardina-ui.github.io/questionarios/SIAS_SPS_v1.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAI — Inventário de Ansiedade de Beck</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Próprio, Mãe, Pai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13–99 anos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mede a intensidade dos sintomas de ansiedade sentidos durante a última semana, incluindo o dia de hoje, em autorrelato de 21 itens numa escala 0–3 (0 = absolutamente não; 1 = levemente, não me incomodou muito; 2 = moderadamente, foi muito desagradável mas pude suportar; 3 = gravemente, dificilmente pude suportar). Total 0–63, com limiares de Beck e Steer (1990/1993): 0–7 mínima, 8–15 ligeira, 16–25 moderada, 26–63 grave. A validação portuguesa (Quintão, Delgado e Prieto, 2013) confirma estrutura UNIDIMENSIONAL, pelo que apenas o total tem cotação normativa; os quatro agrupamentos de sintomas são exploratórios, as alocações de itens divergem entre estudos e são apresentados em escala descritiva azul, sem juízo de gravidade. O instrumento sobrerrepresenta deliberadamente a componente SOMÁTICA da ansiedade, o que o torna útil para discriminar ansiedade de depressão mas insuficiente como medida isolada de ansiedade cognitiva ou de preocupação. É de autopreenchimento e mede a ansiedade de QUEM PREENCHE: aplicado a um progenitor, o resultado descreve o progenitor e não a criança; o código do paciente identifica o processo, não o sujeito da medida. Entre aplicações, apenas diferenças iguais ou superiores a 7 pontos constituem mudança fiável (índice de mudança fiável, Seggar et al., 2002); variações menores situam-se dentro do erro de medida. Instrumento proprietário (© Beck / Psychological Corporation), tradução portuguesa autorizada. Resultado isolado não é diagnóstico.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total BAI (0–63) — única saída com cotação normativa; limiares 0–7 mínima, 8–15 ligeira, 16–25 moderada, 26–63 grave; Agrupamento subjetivo, 7 itens (0–21) — incapaz de relaxar, medo que aconteça o pior, aterrorizado, nervoso, medo de perder o controlo, medo de morrer, assustado; Agrupamento neurofisiológico, 6 itens (0–18) — tremores nas pernas e nas mãos, trémulo, sem equilíbrio, sensação de sufocação, dificuldade de respirar; Agrupamento autonómico, 4 itens (0–12) — palpitação ou aceleração do coração, sensação de calor, indigestão ou desconforto abdominal, rosto afogueado; Agrupamento de pânico, 4 itens (0–12) — dormência ou formigamento, atordoado ou tonto, sensação de desmaio, suor não devido ao calor; Comparação longitudinal pelo índice de mudança fiável (diferença igual ou superior a 7 pontos entre aplicações)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q_bai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://correiaricardina-ui.github.io/questionarios/BAI_v1.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BDI-II — Inventário de Depressão de Beck II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mede a gravidade dos sintomas depressivos sentidos durante as duas últimas semanas, incluindo o dia de hoje, em autorrelato de 21 grupos de afirmações cotados 0–3. Total 0–63, com limiares de Beck, Steer e Brown (1996): 0–13 mínima, 14–19 ligeira, 20–28 moderada, 29–63 grave. Versão portuguesa de Quelhas Martins e Coelho (Faculdade de Medicina do Porto, 2000). Numa amostra comunitária portuguesa a média foi 11,01 (desvio-padrão 9,15; N = 2401; Oliveira-Brochado, Simões e Paúl, 2014): referência DESCRITIVA de enquadramento, nunca convertida em percentil nem em score padronizado. O ITEM 9 (pensamentos ou desejos suicidas) constitui sinalizador clínico próprio: qualquer cotação igual ou superior a 1 exige avaliação directa de ideação e risco, independentemente do total, e é registada em coluna separada no Sheet para permitir filtragem. Os grupos 16 (sono) e 18 (apetite) têm 7 opções cotadas 0-1-1-2-2-3-3, em que aumento e diminuição pontuam igual mas são clinicamente opostos: o sistema guarda a opção assinalada e não apenas a pontuação. As duas dimensões bifatoriais não têm cotação normativa própria e existem modelos factoriais alternativos, pelo que são apresentadas em escala descritiva azul. Assume o formulário BDI-II, cujos itens e ordem diferem do BDI original. É de autopreenchimento e mede a depressão de QUEM PREENCHE: aplicado a um progenitor, o resultado descreve o progenitor e não a criança. Instrumento proprietário (© Beck / Psychological Corporation). Resultado isolado não é diagnóstico.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total BDI-II (0–63) — única saída com cotação normativa; limiares 0–13 mínima, 14–19 ligeira, 20–28 moderada, 29–63 grave; Dimensão cognitivo-afetiva, itens 1 a 13 (0–39) — tristeza, pessimismo, fracassos passados, perda de prazer, sentimentos de culpa, sentimentos de punição, autodepreciação, autocriticismo, pensamentos ou desejos suicidas, choro, agitação, perda de interesse, indecisão; Dimensão somática, itens 14 a 21 (0–24) — sentimentos de inutilidade, perda de energia, alterações no padrão de sono, irritabilidade, alterações no apetite, dificuldades de concentração, cansaço ou fadiga, perda de interesse sexual; Predomínio relativo entre as duas dimensões (cognitivo-afetivo, somático ou equilibrado) — descritor de configuração, sem cotação normativa própria; Sinalizador clínico — item 9, pensamentos ou desejos suicidas: qualquer cotação igual ou superior a 1 exige avaliação directa de ideação e risco, independentemente do total; Referência comunitária portuguesa para enquadramento descritivo: média 11,01, desvio-padrão 9,15 (Oliveira-Brochado, Simões e Paúl, 2014)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bdi2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q_bdi2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://correiaricardina-ui.github.io/questionarios/BDI2_v1.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSWQ — Questionário de Preocupação do Estado da Pensilvânia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18–99 anos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mede a preocupação enquanto TRAÇO — intensidade, generalização e incontrolabilidade — em autorrelato de 16 itens numa escala 1–5; não avalia o conteúdo temático da preocupação. Itens 1, 3, 8, 10 e 11 invertidos, pelo que o mínimo empírico do total é 36 e o máximo 60. Âncora normativa primária: comunidade portuguesa de Oliveira et al. (2021). Critério c de significância clínica 57,40 → 58; mudança fiável a partir de 8 pontos (RCI 95% = 7,93). Os cortes internacionais 45/62/65 são apenas marcadores comparativos, nunca critério de classificação. Mede a preocupação de QUEM PREENCHE; validado para adultos (≥ 18 anos) — em idade pediátrica usar o PSWQ-C.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total PSWQ (16–80; mínimo empírico 36, máximo empírico 60) — z e percentil face à comunidade portuguesa de Oliveira et al. (2021), n = 256, M = 50,91, DP = 9,86; Banda descritiva de posicionamento normativo (marcadamente abaixo, abaixo, dentro do intervalo médio comunitário, acima, marcadamente acima da média comunitária); Escala Positiva PSWQ-11, 11 itens diretos (11–55) — norma de Freitas (2017), n = 90, M = 34,79, DP = 8,74; Bloco de itens invertidos em métrica bruta, F2b, 5 itens (5–25) — norma de Freitas (2017), M = 12,06, DP = 4,11; valores mais BAIXOS indicam maior preocupação; Bloco de itens invertidos em métrica cotada, F2c (5–25) — 30 − F2b, apenas para conferência da soma; Média por item (1,00–5,00); Posicionamento comparativo noutras distribuições de referência (clínica portuguesa, comunidade portuguesa secundária, não clínica dos EUA, Perturbação de Ansiedade Generalizada agregada); Sinalizador clínico — critério c de Jacobson &amp; Truax (57,40 → 58); Sinalizador de aplicabilidade — alerta etário automático abaixo dos 18 anos; Indicador exploratório de coerência entre blocos, |z(F1) + z(F2b)|, limiar 2,00; Monitorização longitudinal pelo índice de mudança fiável (Δ ≥ 8 pontos; RCI 95% = 7,93)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pswq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q_pswq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://correiaricardina-ui.github.io/questionarios/PSWQ_v1.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRIEF-A — Autorrelato</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18–90 anos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avalia o funcionamento executivo no quotidiano do adulto em 75 itens, numa escala de frequência de três pontos (Nunca = 1; Às vezes = 2; Frequentemente = 3), reportada ao último mês. RECOLHE EXCLUSIVAMENTE PONTUAÇÕES BRUTAS, por resposta e por escala: nove escalas clínicas, os índices BRI, MI e GEC, e as duas escalas de validade. Por decisão clínica NÃO converte para T-score nem para percentil — a leitura normativa, que depende da idade e do sexo, é feita manualmente nas tabelas do manual a partir da folha de cotação exportada em PDF, que traz as colunas T e Percentil em branco. Os itens 10, 27, 38, 48 e 59 pertencem à escala de Infrequência e não entram em nenhuma escala clínica (70 itens clínicos + 5 de validade). No painel, escalas e índices são apresentados em escala descritiva azul, com a posição do valor bruto dentro da amplitude possível; o vermelho fica reservado aos dois sinalizadores binários de validade. T ≥ 65 é o limiar tradicionalmente considerado clinicamente elevado no BRIEF-A, mas essa leitura só existe depois da conversão manual. Instrumento proprietário (Roth, Isquith e Gioia, 2005; PAR). Resultado isolado não é diagnóstico. Versão de AUTORRELATO: descreve o funcionamento executivo tal como o próprio o relata.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inibição (8 itens, 8–24); Flexibilidade (6 itens, 6–18); Controlo Emocional (10 itens, 10–30); Automonitorização (6 itens, 6–18); Iniciativa (8 itens, 8–24); Memória de Trabalho (8 itens, 8–24); Planificação/Organização (10 itens, 10–30); Monitorização da Tarefa (6 itens, 6–18); Organização de Materiais (8 itens, 8–24); BRI — Índice de Regulação Comportamental (Inibição + Flexibilidade + Controlo Emocional + Automonitorização; 30 itens, 30–90); MI — Índice de Metacognição (Iniciativa + Memória de Trabalho + Planificação/Organização + Monitorização da Tarefa + Organização de Materiais; 40 itens, 40–120); GEC — Composto Executivo Global (BRI + MI; 70 itens, 70–210); Infrequência — escala de validade (5 itens: 10, 27, 38, 48 e 59; 0–5; 0–2 aceitável, ≥3 sinaliza padrão de resposta infrequente); Inconsistência — escala de validade (10 pares de itens equivalentes: 2–41, 25–49, 28–42, 33–72, 34–63, 44–61, 46–56, 52–75, 60–74, 64–70; soma das diferenças absolutas, 0–20; 0–7 aceitável, ≥8 sinaliza inconsistência)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brief_a_auto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q_brief_a_auto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://correiaricardina-ui.github.io/questionarios/BRIEF_A_Autorrelato_v1.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRIEF-A — Informante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mãe, Pai, Outro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avalia o funcionamento executivo no quotidiano do adulto em 75 itens, numa escala de frequência de três pontos (Nunca = 1; Às vezes = 2; Frequentemente = 3), reportada ao último mês. RECOLHE EXCLUSIVAMENTE PONTUAÇÕES BRUTAS, por resposta e por escala: nove escalas clínicas, os índices BRI, MI e GEC, e as duas escalas de validade. Por decisão clínica NÃO converte para T-score nem para percentil — a leitura normativa, que depende da idade e do sexo, é feita manualmente nas tabelas do manual a partir da folha de cotação exportada em PDF, que traz as colunas T e Percentil em branco. Os itens 10, 27, 38, 48 e 59 pertencem à escala de Infrequência e não entram em nenhuma escala clínica (70 itens clínicos + 5 de validade). No painel, escalas e índices são apresentados em escala descritiva azul, com a posição do valor bruto dentro da amplitude possível; o vermelho fica reservado aos dois sinalizadores binários de validade. T ≥ 65 é o limiar tradicionalmente considerado clinicamente elevado no BRIEF-A, mas essa leitura só existe depois da conversão manual. Instrumento proprietário (Roth, Isquith e Gioia, 2005; PAR). Resultado isolado não é diagnóstico. Versão de INFORMANTE: preenchida por alguém que conhece bem a pessoa avaliada (cônjuge, familiar, amigo ou cuidador), paralela ao autorrelato item a item, para triangulação entre a descrição do próprio e a do informante.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brief_a_inf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q_brief_a_inf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://correiaricardina-ui.github.io/questionarios/BRIEF_A_Informante_v1.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESS — Escala de Sonolência de Epworth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rastreio da sonolência diurna excessiva por autorrelato (Johns, 1991; versão portuguesa CEISUC/LEPS, 2001). 8 itens, escala ordinal 0–3, todos directos — sem itens invertidos e sem ponderações; total = soma simples (0–24). Mede a propensão média para ADORMECER em situações quotidianas de baixa e média ativação, tomando como referência o modo de vida habitual no período recente: não mede fadiga, cansaço subjetivo, sonolência momentânea no ato de resposta nem qualidade do sono. Coexistem três sistemas interpretativos e nenhum foi suprimido: Sistema A como referência primária (0–7 sonolência normal · 8–10 sonolência média · 11–15 sonolência excessiva moderada · 16–24 sonolência excessiva grave); critério dicotómico impresso no formulário da versão portuguesa, total ≥ 10; bandas de Johns (0–5 · 6–10 · 11–12 · 13–15 · 16–24). Os dois primeiros divergem EXCLUSIVAMENTE na pontuação 10, em que o Sistema A mantém «Sonolência média» e o critério português é positivo — divergência assinalada automaticamente e não resolvida pelo sistema (anomalia A-01); a escolha da referência a reportar é clínica. NÃO existem normas portuguesas por idade e sexo: não são gerados percentis nem T-scores (anomalia A-04). Validada para ADULTOS (≥ 18 anos) — abaixo dos 18 usar a ESS-CHAD (Janssen et al., 2017); o painel emite alerta etário automático. Instrumento de autopreenchimento: mede a sonolência de QUEM PREENCHE, pelo que aplicada a um progenitor descreve o progenitor e não a criança — o código do paciente identifica o processo, não o sujeito da medida. Completude: 8/8 itens para protocolo válido (R3); com 6 ou 7 itens gera estimativa pró-rateada [(soma / n) × 8, arredondada], exploratória e não comparável a normas (R4); abaixo de 6 itens não produz pontuação (R5); o item 8 (ao volante) pressupõe a condição de condutor e, em não condutores, fica em branco com pró-rateio e comparabilidade «Limitada» (R6). Medida de RASTREIO: não diagnostica apneia obstrutiva do sono, narcolepsia, hipersonolência idiopática nem privação crónica de sono, e não substitui a avaliação médica do sono nem o estudo polissonográfico — uma pontuação baixa não exclui patologia do sono e uma pontuação elevada não estabelece a sua etiologia.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pontuação total ESS (0–24) — única saída com cotação; instrumento unidimensional, sem subescalas; Classificação pelo Sistema A, referência primária (0–7 sonolência normal · 8–10 sonolência média · 11–15 sonolência excessiva moderada · 16–24 sonolência excessiva grave); Critério dicotómico da versão portuguesa CEISUC/LEPS (2001), coincidente com o critério original de Johns (1991) — total ≥ 10 indica sonolência diurna excessiva; Bandas de referência de Johns, Sistema C (0–5 normal baixa · 6–10 normal elevada · 11–12 excessiva ligeira · 13–15 excessiva moderada · 16–24 excessiva grave), reportadas em paralelo para rastreabilidade bibliográfica; Concordância entre sistemas — assinala a divergência única na pontuação 10 (anomalia A-01), sem a resolver; Natureza da pontuação — distinção entre valor observado (8/8 itens) e estimativa pró-rateada (6–7 itens), esta última não comparável a normas; Validade do protocolo — regras R3 (8/8 válido), R4 (6–7 itens, pró-rateio), R5 (&lt; 6 itens, sem pontuação) e R6 (item 8 não aplicável a não condutores); Comparabilidade normativa — «Aplicável» apenas com protocolo completo e item 8 aplicável, caso contrário «Limitada» ou «Não aplicável»; Agrupamento descritivo exploratório G1, situações de baixa ativação (itens 1–5; 0–15) — estritamente descritivo, sem normas nem pontos de corte (R7), não reportar como subescala; Agrupamento descritivo exploratório G2, situações de ativação intermédia a elevada (itens 6–8; 0–9) — estritamente descritivo, sem normas nem pontos de corte (R7), não reportar como subescala; Diferencial G2 − G1 (médias por item) — valor positivo indica propensão a adormecer também em situações de maior ativação; indicador descritivo, sem ponto de corte; Indicadores de padrão — pontuação máxima num item, número de itens cotados em 3, em ≥ 2 e em 0; Sinalizador descritivo de contexto de veículo (soma dos itens 4 e 8 ≥ 4, de um máximo de 6) — orienta a entrevista quanto a segurança rodoviária e não constitui juízo sobre aptidão para conduzir; Sinalizador de aplicabilidade etária — alerta automático quando a idade de quem responde é inferior a 18 anos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ess</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q_ess</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://correiaricardina-ui.github.io/questionarios/ESS_Epworth_v1.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STOP-BANG — Rastreio de Risco de Apneia Obstrutiva do Sono</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rastreio do RISCO de síndrome de apneia obstrutiva do sono por acumulação de oito fatores binários — quatro sintomáticos (bloco STOP: ressonar, cansaço ou sonolência diurna, apneias observadas, hipertensão arterial) e quatro objetivos (bloco BANG: índice de massa corporal, idade, perímetro cervical, sexo). Total 0–8, soma simples e sem ponderações. ⚠ NÃO é um formulário auto-administrado: o STOP-BANG é um instrumento PROPRIETÁRIO (Frances Chung e University Health Network, Toronto; www.stopbang.ca) e a ficha foi construída em VIA A-RESTRITA — reproduz apenas as designações dos domínios do acrónimo e os critérios operacionais objetivos, que constituem factos clínicos e não expressão protegida, e NÃO reproduz os enunciados dos itens. A ampla circulação pública do questionário não equivale a licença de redistribuição, e a publicação da validação portuguesa (Reis et al., 2015) não transfere direitos sobre o instrumento. Opera em complemento do formulário original em uso no serviço, do qual o profissional transcreve as quatro respostas do bloco STOP; os quatro indicadores do bloco BANG são derivados automaticamente dos dados clínicos brutos (idade, sexo, peso, altura, perímetro cervical), com os critérios IMC &gt; 35 kg/m², idade &gt; 50 anos, perímetro cervical acima do limiar e sexo masculino. O perímetro cervical é cotado por DOIS critérios em paralelo: o critério português, &gt; 40 cm e indiferenciado por sexo (Reis et al., 2015, e versão original de 2008), que constitui a pontuação PRINCIPAL, e o critério da versão atual do detentor, masculino ≥ 43 cm e feminino ≥ 41 cm, que funciona como verificação de concordância — a divergência entre os dois totais é assinalada e NÃO é resolvida automaticamente, cabendo ao clínico a escolha do critério a reportar. Classificação em dois níveis: bandas do documento-fonte (0–2 risco baixo · 3–4 risco intermédio · ≥ 5 risco elevado) e, sobre estas, o refinamento da faixa intermédia de Chung, Abdullah &amp; Liao (Chest, 2016), que reclassifica como risco elevado as pontuações 3–4 com STOP ≥ 2 e pelo menos um de IMC, perímetro cervical ou sexo masculino positivos. As probabilidades previstas provêm de regressão logística numa amostra portuguesa de clínica do sono (Reis et al., 2015) e existem publicadas apenas para as pontuações 3 a 6 (qualquer grau) e 6 a 8 (forma grave); as restantes apresentam «n.d.», sem qualquer interpolação — e, tratando-se de uma população com prevalência de base elevada, a sua transposição para rastreio comunitário ou cuidados de saúde primários SOBRESTIMA o risco. ⚠ Validado exclusivamente em população ADULTA (≥ 18 anos): os critérios «idade &gt; 50» e «IMC &gt; 35» carecem de significado em idade pediátrica, onde os preditores de apneia obstrutiva são distintos (hipertrofia adenoamigdalina como fator dominante); o ficheiro bloqueia a introdução de idades inferiores a 18 anos. ⚠ Índice FORMATIVO de acumulação de fatores de risco e não escala reflexiva de um construto latente: os oito indicadores são causas do estatuto de risco e não manifestações de uma dimensão comum, pelo que os coeficientes de consistência interna (alfa, ómega) e a análise fatorial dos itens são metodologicamente inaplicáveis, e não existem subescalas — STOP e BANG são blocos de contagem. ⚠ Instrumento de RASTREIO: sensibilidade elevada (93,4% para IAH ≥ 5 no ponto de corte ≥ 3) e especificidade baixa (48,9% no mesmo corte), pelo que se destina a EXCLUIR com segurança e não a confirmar — uma classificação de risco elevado indica probabilidade acrescida e justifica referenciação para avaliação especializada, não estabelecendo por si o diagnóstico, que exige estudo do sono.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pontuação total pelo critério português (0–8) — saída principal; soma dos oito indicadores binários, sem ponderações; Subtotal do bloco STOP, itens 1–4, indicadores sintomáticos (0–4) — bloco de contagem, NÃO subescala; Subtotal do bloco BANG, itens 5–8, indicadores objetivos (0–4) — bloco de contagem, NÃO subescala; Cotação item a item — Ressonar (S), Cansaço ou sonolência diurna (T), Apneias observadas (O), Hipertensão arterial (P), Índice de massa corporal (B), Idade (A), Perímetro cervical (N), Sexo (G); Índice de massa corporal derivado automaticamente do peso e da altura (kg/m²), com o critério operacional &gt; 35; Cotação paralela do perímetro cervical — critério português &gt; 40 cm indiferenciado por sexo (principal) e critério da University Health Network, masculino ≥ 43 cm e feminino ≥ 41 cm (verificação); Pontuação total pelo critério UHN (0–8) — cálculo paralelo, exclusivamente para verificação de concordância; Concordância entre critérios de perímetro cervical — assinala a divergência quando os dois totais diferem, sem a resolver; Nível 1 · Banda de risco do documento-fonte (0–2 risco baixo · 3–4 risco intermédio · ≥ 5 risco elevado); Nível 2 · Classificação final com refinamento da faixa intermédia (Chung, Abdullah &amp; Liao, 2016) — pontuação 3–4 com STOP ≥ 2 e IMC, perímetro cervical ou sexo masculino positivos passa a «Risco elevado (reclassificado)»; Classificação paralela pelo critério UHN — mesmas bandas aplicadas ao total do critério diferenciado por sexo; Probabilidade prevista de SAOS de qualquer grau (Reis et al., 2015) — publicada apenas para as pontuações 3 a 6 (64%, 80%, 90%, 95%); restantes «n.d.», sem interpolação; Probabilidade prevista de SAOS grave, IAH ≥ 30 (Reis et al., 2015) — publicada apenas para as pontuações 6 a 8 (46%, 61%, 73%); restantes «n.d.», sem interpolação; Elegibilidade etária — sinalizador de bloqueio automático abaixo dos 18 anos, por o instrumento não estar validado em idade pediátrica; Estado do protocolo — a cotação só é produzida com a totalidade dos dados clínicos objetivos e das quatro respostas do bloco STOP.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stopbang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q_stopbang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://correiaricardina-ui.github.io/questionarios/STOPBANG_v1.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EII-27 · Forma A — Escala de Intolerância à Incerteza (versão longa, adultos)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mede a INTOLERÂNCIA À INCERTEZA — o conjunto de crenças negativas segundo as quais a ambiguidade é inaceitável, ameaçadora e geradora de sofrimento, independentemente da probabilidade objetiva de um desfecho negativo. Autorrelato de 27 itens numa escala 1–5 (1 = nada característico de mim → 5 = totalmente característico de mim), TODOS no sentido directo: não existe um único item invertido. Total 27–135, com estrutura bifatorial de Sexton &amp; Dugas (2009) — F1 «a incerteza tem implicações negativas comportamentais e auto-referentes» (15 itens, 15–75) e F2 «a incerteza é injusta e estraga tudo» (12 itens, 12–60). Sendo a versão de 12 itens um subconjunto ESTRITO desta (itens 7, 8, 9, 10, 11, 12, 15, 18, 19, 20, 21 e 25), uma só administração devolve também as três escalas curtas derivadas — EII-12 Total, Ansiedade Prospetiva e Ansiedade Inibitória. Construto TRANSDIAGNÓSTICO, central no modelo cognitivo da ansiedade generalizada de Dugas e Ladouceur e associado à perturbação obsessivo-compulsiva, à ansiedade social, ao pânico, à ansiedade de doença, às perturbações do comportamento alimentar e à sintomatologia depressiva; não constitui, em si, critério de diagnóstico de qualquer entidade do DSM-5-TR ou da CID-11. ⚠ Tradução técnica de trabalho para português europeu (Via A), SEM retroversão independente, SEM painel de peritos, SEM pré-teste cognitivo e SEM estudo psicométrico em amostra nacional: fidelidade, validade e estrutura fatorial não estão verificadas nesta versão. ⚠ NÃO existem normas portuguesas e NÃO são aplicados pontos de corte — toda a leitura é feita em POMP, percentagem da amplitude teórica, com bandas descritivas por quintis que situam a pontuação no intervalo possível do instrumento e NÃO medem gravidade clínica. ⚠ Instrumento desenvolvido e normalizado em população ADULTA: a Forma J é adaptação de registo linguístico para os 12–17 anos, sem estudo de equivalência de medida, pelo que as pontuações das duas formas não são comparáveis entre si e a forma deve manter-se constante ao longo do acompanhamento do mesmo caso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total EII-27 (27–135) — pontuação global de intolerância à incerteza; reportada em POMP e banda descritiva, sem norma e sem ponto de corte; Fator 1 — a incerteza tem implicações negativas comportamentais e auto-referentes (15 itens, 15–75; itens 1, 2, 3, 9, 12, 13, 14, 15, 16, 17, 20, 22, 23, 24, 25); inclui o eixo auto-referente (competência pessoal, comparação social, confiança em si) que NÃO está representado na versão curta; Fator 2 — a incerteza é injusta e estraga tudo (12 itens, 12–60; itens 4, 5, 6, 7, 8, 10, 11, 18, 19, 21, 26, 27); EII-12 Total derivada (12–60) — calculada automaticamente a partir dos itens 7, 8, 9, 10, 11, 12, 15, 18, 19, 20, 21 e 25 da versão longa; Ansiedade Prospetiva derivada (7 itens, 7–35) — orientação apreensiva para o futuro: necessidade de antecipação, de previsibilidade e de informação completa; Ansiedade Inibitória derivada (5 itens, 5–25) — paralisação da ação, adiamento e evitamento perante a ambiguidade; POMP por escala (0–100) — (pontuação − mínimo) ÷ (máximo − mínimo) × 100; métrica comum que permite comparar escalas de amplitudes diferentes, transformação linear e integralmente reversível, sem qualquer pressuposto normativo; Banda descritiva por quintis da amplitude teórica — Muito baixa (0–20) · Baixa (20–40) · Moderada (40–60) · Elevada (60–80) · Muito elevada (80–100); descreve POSIÇÃO no intervalo possível, nunca gravidade clínica; Diferenciação intra-individual Δ POMP entre Ansiedade Prospetiva e Inibitória — Perfil equilibrado (0–10) · Diferenciação ligeira (10–20) · Diferenciação marcada (≥ 20), com identificação do polo relativamente mais elevado; convenção descritiva sem suporte empírico publicado, exclusivamente intra-individual e NUNCA comparativa entre sujeitos; Tratamento de omissões por prorrateamento — máximo de 2 omissões no total da EII-27, 1 em F1, F2, EII-12 Total e Ansiedade Prospetiva, e 0 na Ansiedade Inibitória (escala demasiado curta para imputação); dentro do limite a pontuação é prorrateada pela média dos itens respondidos da própria escala, acima do limite a escala é declarada NÃO COTÁVEL sem qualquer estimativa, escala a escala; Controlo de qualidade do protocolo — desvio-padrão dos itens cotados, com sinalizador de padrão de resposta invariante (desvio-padrão nulo) que exige ponderar a validade do protocolo antes de qualquer leitura; Tabela de normas parametrizável — a partir do momento em que sejam introduzidas médias e desvios-padrão de referência aplicáveis, o sistema passa a calcular scores z e percentis estimados; até lá essas saídas permanecem vazias por construção, em vez de apresentarem valores sem fundamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eii27_a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q_eii27_a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://correiaricardina-ui.github.io/questionarios/EII27_A_v1.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EII-27 · Forma J — Escala de Intolerância à Incerteza (versão longa, adolescentes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12–17 anos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eii27_j</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q_eii27_j</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://correiaricardina-ui.github.io/questionarios/EII27_J_v1.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EII-12 · Forma A — Escala de Intolerância à Incerteza (versão curta, adultos)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Versão curta da Escala de Intolerância à Incerteza (Carleton, Norton &amp; Asmundson, 2007), destinada a rastreio, a monitorização repetida ao longo do acompanhamento e a protocolos extensos ou com adolescentes, em que a carga de resposta é uma preocupação. Autorrelato de 12 itens numa escala 1–5, TODOS no sentido directo — não existe um único item invertido. Total 12–60, com duas subescalas: Ansiedade Prospetiva (7 itens, 7–35), que descreve a orientação apreensiva para o futuro e a necessidade de antecipação, de previsibilidade e de informação completa, e Ansiedade Inibitória (5 itens, 5–25), que descreve a paralisação da ação, o adiamento e o evitamento perante a ambiguidade. Parte da literatura recomenda a leitura PREFERENCIAL do total, sustentando a existência de um fator geral robusto, pelo que a leitura por subescalas deve ser tomada como complementar e intra-individual. Tempo de aplicação de 3 a 5 minutos. ⚠ Tradução técnica de trabalho para português europeu (Via A), SEM retroversão independente e SEM estudo psicométrico em amostra nacional. ⚠ NÃO existem normas portuguesas e NÃO são aplicados pontos de corte — toda a leitura é feita em POMP e bandas descritivas por quintis da amplitude teórica, que situam a pontuação no intervalo possível do instrumento e NÃO medem gravidade clínica. ⚠ Desenvolvida e normalizada em população ADULTA: a Forma J é adaptação de registo linguístico para os 12–17 anos, sem estudo de equivalência de medida, e as pontuações das duas formas não são comparáveis entre si. ⚠ Administrada isoladamente, esta versão pode apresentar propriedades distintas das obtidas quando derivada da EII-27, por efeito de contexto de resposta: em monitorização longitudinal, manter sempre a mesma via de obtenção e não alternar entre a versão curta e a longa a meio do acompanhamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total EII-12 (12–60) — saída principal, com leitura preferencial sobre as subescalas; reportado em POMP e banda descritiva, sem norma e sem ponto de corte; Ansiedade Prospetiva (7 itens, 7–35) — orientação apreensiva para o futuro: necessidade de antecipação, de previsibilidade e de informação completa; procura de informação, planeamento e verificação; Ansiedade Inibitória (5 itens, 5–25) — paralisação da ação, adiamento e evitamento perante a ambiguidade; POMP por escala (0–100) — (pontuação − mínimo) ÷ (máximo − mínimo) × 100; métrica comum que permite comparar escalas de amplitudes diferentes, sem qualquer pressuposto normativo; Banda descritiva por quintis da amplitude teórica — Muito baixa (0–20) · Baixa (20–40) · Moderada (40–60) · Elevada (60–80) · Muito elevada (80–100); descreve POSIÇÃO no intervalo possível, nunca gravidade clínica; Diferenciação intra-individual Δ POMP entre Ansiedade Prospetiva e Inibitória — Perfil equilibrado (0–10) · Diferenciação ligeira (10–20) · Diferenciação marcada (≥ 20), com identificação do polo relativamente mais elevado; convenção descritiva sem suporte empírico publicado, exclusivamente intra-individual; Tratamento de omissões por prorrateamento — máximo de 1 omissão no total e na Ansiedade Prospetiva e 0 na Ansiedade Inibitória; acima do limite a escala é declarada NÃO COTÁVEL, sem qualquer estimativa; Controlo de qualidade do protocolo — desvio-padrão dos itens cotados, com sinalizador de padrão de resposta invariante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eii12_a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q_eii12_a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://correiaricardina-ui.github.io/questionarios/EII12_A_v1.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EII-12 · Forma J — Escala de Intolerância à Incerteza (versão curta, adolescentes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eii12_j</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q_eii12_j</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://correiaricardina-ui.github.io/questionarios/EII12_J_v1.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAARS–S:L — Conners’ Adult ADHD Rating Scales (forma longa, auto-relato)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avalia a sintomatologia de Perturbação de Hiperatividade e Défice de Atenção no ADULTO através da forma longa das Conners’ Adult ADHD Rating Scales (Conners, Erhardt &amp; Sparrow, 1999; Multi-Health Systems Inc.). 66 itens numa escala 0–3 (0 = nada, nunca → 3 = muito, muito frequentemente), TODOS no sentido directo — não existe um único item invertido. Devolve oito resultados brutos: quatro escalas factoriais (A Problemas de Desatenção/Memória, B Hiperatividade/Inquietação, C Impulsividade/Labilidade Emocional, D Problemas com o Autoconceito), as duas listas de sintomas do DSM-IV (E Desatenção, F Hiperatividade-Impulsividade) e as suas derivadas (G Sintomas Totais de PHDA = E + F, H Índice de PHDA), mais o Índice de Inconsistência. ⚠ A conversão de resultado bruto em T-score NÃO é feita pela plataforma: as tabelas normativas são propriedade do editor (MHS) e a leitura faz-se nas folhas de perfil oficiais, pelo SEXO e IDADE DA PESSOA AVALIADA — nunca do observador. O T é introduzido manualmente no painel clínico do questionário, onde activa as bandas descritivas (45 · 56 · 60 · 65 · 70) e a interpretação; sem T introduzido o painel apresenta apenas resultados brutos e percentagem do máximo, em paleta azul e sem juízo de gravidade. ⚠ As bandas são convenções interpretativas, NÃO pontos de corte diagnósticos: o DSM-5-TR exige início antes dos 12 anos, presença em pelo menos dois contextos e interferência funcional. ⚠ Nenhuma das formas é padrão-ouro face à outra — a divergência entre auto-relato e heterorrelato é dado clínico a interpretar, não critério de validade. ⚠ Índice de Inconsistência ≥ 8 exige prudência interpretativa quanto à consistência do protocolo. ⚠ Instrumento sob licença (MHS): utilização reservada a quem detenha protocolo oficial e o manual. Forma de AUTO-RELATO: é a própria pessoa avaliada que descreve o seu funcionamento recente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A — Problemas de Desatenção/Memória (12 itens, RB 0–36): esquecimento, desorganização, dificuldade em iniciar e concluir tarefas, má estimativa do tempo | B — Hiperatividade/Inquietação (12 itens, RB 0–36): inquietação motora e interna, procura de estimulação, dificuldade em permanecer parado | C — Impulsividade/Labilidade Emocional (12 itens, RB 0–36): dizer e agir sem pensar, irritabilidade, oscilações de humor, baixa tolerância à frustração | D — Problemas com o Autoconceito (6 itens, RB 0–18): insegurança, baixa confiança nas próprias capacidades, peso dos fracassos anteriores | E — Sintomas de Desatenção do DSM-IV (9 itens, RB 0–27): correspondência item a item com o critério A1 | F — Sintomas de Hiperatividade-Impulsividade do DSM-IV (9 itens, RB 0–27): correspondência item a item com o critério A2 | G — Sintomas Totais de PHDA do DSM-IV (18 itens, RB 0–54): derivada por soma de E + F, sem itens próprios | H — Índice de PHDA (12 itens, RB 0–36): itens que melhor discriminam adultos com e sem o diagnóstico; escala de rastreio | Índice de Inconsistência (0–24): soma dos diferenciais absolutos em 8 pares de itens de conteúdo equivalente (11-49, 40-44, 20-25, 13-27, 30-47, 19-23, 6-37, 26-63); ≥ 8 exige prudência interpretativa | Grupo normativo derivado da idade da pessoa avaliada — 1: 18–29 · 2: 30–39 · 3: 40–49 · 4: ≥ 50 anos; as folhas de perfil são ainda separadas por sexo (M1–M4 / F1–F4) | Bandas descritivas por T-score, comuns às duas formas — Abaixo da média (&lt; 45) · Média (45–55) · Ligeiramente atípico (56–59) · Ligeiramente elevado (60–64) · Elevado (65–69) · Muito elevado (≥ 70) | Seis itens pertencem simultaneamente a duas escalas (19, 23, 26, 27, 40 e 63): 72 atribuições item→escala para 66 itens — soma de controlo do protocolo de cotação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">caars_sl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q_caars_sl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://correiaricardina-ui.github.io/questionarios/CAARS_SL_v1.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAARS–O:L — Conners’ Adult ADHD Rating Scales (forma longa, heterorrelato)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cônjuge/Parceiro(a), Familiar, Mãe, Pai, Outro familiar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avalia a sintomatologia de Perturbação de Hiperatividade e Défice de Atenção no ADULTO através da forma longa das Conners’ Adult ADHD Rating Scales (Conners, Erhardt &amp; Sparrow, 1999; Multi-Health Systems Inc.). 66 itens numa escala 0–3 (0 = nada, nunca → 3 = muito, muito frequentemente), TODOS no sentido directo — não existe um único item invertido. Devolve oito resultados brutos: quatro escalas factoriais (A Problemas de Desatenção/Memória, B Hiperatividade/Inquietação, C Impulsividade/Labilidade Emocional, D Problemas com o Autoconceito), as duas listas de sintomas do DSM-IV (E Desatenção, F Hiperatividade-Impulsividade) e as suas derivadas (G Sintomas Totais de PHDA = E + F, H Índice de PHDA), mais o Índice de Inconsistência. ⚠ A conversão de resultado bruto em T-score NÃO é feita pela plataforma: as tabelas normativas são propriedade do editor (MHS) e a leitura faz-se nas folhas de perfil oficiais, pelo SEXO e IDADE DA PESSOA AVALIADA — nunca do observador. O T é introduzido manualmente no painel clínico do questionário, onde activa as bandas descritivas (45 · 56 · 60 · 65 · 70) e a interpretação; sem T introduzido o painel apresenta apenas resultados brutos e percentagem do máximo, em paleta azul e sem juízo de gravidade. ⚠ As bandas são convenções interpretativas, NÃO pontos de corte diagnósticos: o DSM-5-TR exige início antes dos 12 anos, presença em pelo menos dois contextos e interferência funcional. ⚠ Nenhuma das formas é padrão-ouro face à outra — a divergência entre auto-relato e heterorrelato é dado clínico a interpretar, não critério de validade. ⚠ Índice de Inconsistência ≥ 8 exige prudência interpretativa quanto à consistência do protocolo. ⚠ Instrumento sob licença (MHS): utilização reservada a quem detenha protocolo oficial e o manual. Forma de HETERORRELATO: responde um observador que convive com a pessoa avaliada (cônjuge, progenitor, irmão(ã) ou outro). O tempo e a frequência de contacto são registados no próprio questionário porque um contacto limitado, ou restrito a um único contexto, reduz a validade do perfil.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">caars_ol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q_caars_ol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://correiaricardina-ui.github.io/questionarios/CAARS_OL_v1.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIFP — Escala de Interferência Funcional Pediátrica (Formas C e P)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Funcionamento &amp; Interferência Funcional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Criança/Jovem,Mãe,Pai,Enc. Educação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mede a INTERFERÊNCIA FUNCIONAL atribuída ao problema-alvo em três domínios de vida da criança ou adolescente, na janela dos ÚLTIMOS 7 DIAS. Instrumento ORIGINAL em português europeu (adaptação inspirada, Via B), construído a partir do enquadramento conceptual e da estrutura psicométrica da Child Sheehan Disability Scale (CSDS/CSDS-P; Whiteside, 2009), SEM reprodução de itens, instruções ou ancoragens protegidas. Duas formas na mesma aba: EIFP-C, autorrelato a partir dos 7 anos, 3 itens 0–10 (total 0–30), e EIFP-P, heterorrelato do cuidador, 5 itens 0–10 (total 0–50) em duas subescalas — Subescala I, interferência na vida da criança (2 itens, 0–20), e Subescala II, interferência na vida do cuidador e da família (3 itens, 0–30). O domínio familiar aparece UMA só vez, referido ao agregado. A leitura primária é feita por DOMÍNIO, não pelo total: consideram-se assinalados os domínios com pontuação SUPERIOR a 5 (Williams, 2000), critério que NÃO deve ser confundido com o ponto de corte de Leon et al. (1997), que incide sobre o total e está documentado mas não é aplicado. Um total baixo pode coexistir com interferência extrema num único domínio (ex.: 10 / 0 / 0 = total 10), pelo que o total é sempre leitura secundária. ⚠ As bandas descritivas de intensidade média — Nula · Ligeira · Moderada · Marcada · Extrema — derivam das ancoragens verbais da própria escala de resposta e NÃO constituem pontos de corte clínicos. ⚠ O instrumento mede INTERFERÊNCIA FUNCIONAL atribuída pelo informante: não mede sintomatologia, gravidade sintomática nem etiologia, e discrepâncias entre sintomas e interferência são informação clínica e não erro de medida. ⚠ As pontuações NÃO são comparáveis entre instrumentos da família EIF, por divergirem as janelas temporais, os referentes e as populações-alvo. ⚠ Sem estudo psicométrico próprio e sem normas portuguesas. ⚠ As referências externas (valores z e limiar de mudança fiável) são da CSDS/CSDS-P, instrumento DISTINTO da EIFP, em amostra norte-americana predominantemente caucasiana e de escolaridade parental elevada; nas amostras comunitárias o desvio-padrão iguala ou excede a média, o que indica assimetria positiva severa e efeito de chão, pelo que os valores z NÃO são convertidos em percentis. ⚠ Whiteside não publicou α por subescala: o índice de mudança fiável só é calculável para os totais, e as subescalas ficam n.d. por construção, sem estimativa. ⚠ Os critérios grupais de Sheehan &amp; Sheehan (2008) NÃO são aplicados nesta versão pediátrica, por derivarem de ensaios com adultos. ⚠ A concordância entre informantes é habitualmente modesta na avaliação pediátrica: divergências entre a Forma C e a Forma P são perspetivas distintas, não erro de medida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIFP-C Total (3 itens, 0–30) — autorrelato da criança ou adolescente sobre escola, amigos e casa | EIFP-P Subescala I — interferência na vida da criança (2 itens, 0–20): escolaridade e vida social | EIFP-P Subescala II — interferência na vida do cuidador e da família (3 itens, 0–30): trabalho e vida social do cuidador, e vida familiar do agregado | EIFP-P Total (5 itens, 0–50) | Sinalização por domínio — assinalável se pontuação SUPERIOR a 5; é o critério primário de leitura e reporta-se domínio a domínio, nunca por agregação | Banda descritiva de intensidade média (média por domínio) — Nula (0) · Ligeira (≤3) · Moderada (≤6) · Marcada (≤9) · Extrema (&gt;9); descreve INTENSIDADE MÉDIA declarada, nunca gravidade clínica nem posição normativa | Dispersão do perfil — perfil dissociado quando a amplitude entre domínios do autorrelato é ≥ 5 pontos, indicando que a leitura pelo total subestimaria o compromisso no domínio mais afetado | Bloco complementar de dias — indicador ecológico externo a QUALQUER total, sem entrar em nenhuma pontuação de escala | Regra de omissão sem imputação — o total de uma escala só é calculado se TODOS os seus itens estiverem respondidos; não há prorrateamento nem estimativa | Distribuição da carga percebida — se se concentra na vida da criança, na do cuidador e família, ou se se distribui de forma equilibrada | Convergência entre informantes — comparação entre a média por domínio do autorrelato e a da Subescala I do heterorrelato; divergências são perspetivas distintas, não erro de medida | Índice de mudança fiável individual (ICF; Jacobson &amp; Truax, 1991) entre M1 e M2 — limiar 8,70 no total do autorrelato e 9,90 no total do heterorrelato; NÃO calculável nas subescalas, por ausência de α publicado | Posição face a referências externas (valores z face à amostra comunitária e à amostra clínica da CSDS/CSDS-P) — sem conversão percentílica, por invalidade estatística</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eifp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q_eifp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://correiaricardina-ui.github.io/questionarios/EIFP_v1.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIFA — Escala de Interferência Funcional em Adultos (Formas A e S)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Próprio,Companheiro(a),Familiar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mede a INTERFERÊNCIA FUNCIONAL atribuída ao problema-alvo em três domínios de vida do adulto, na janela dos ÚLTIMOS 7 DIAS. Duas formas na mesma aba: EIFA-A, autorrelato do próprio, 3 itens 0–10 (total 0–30), adaptação inspirada (Via B) da Sheehan Disability Scale (Sheehan, 1983) sem reprodução de conteúdo protegido; e EIFA-S, heterorrelato do companheiro ou outra pessoa significativa, 5 itens 0–10 (total 0–50) em duas subescalas — Subescala I, interferência na vida do próprio (2 itens, 0–20), e Subescala II, interferência na vida do informante e do agregado (3 itens, 0–30) —, esta construção DE RAIZ (Via C), seguindo a solução bifatorial validada por Whiteside (2009) no heterorrelato pediátrico. O domínio familiar aparece UMA só vez, referido ao agregado, porque o casal o partilha. A leitura primária é feita por DOMÍNIO, não pelo total: consideram-se assinalados os domínios com pontuação SUPERIOR a 5 (Williams, 2000), critério que NÃO deve ser confundido com o ponto de corte de Leon et al. (1997), que incide sobre o total e está documentado mas não é aplicado. Um total baixo pode coexistir com interferência extrema num único domínio (ex.: 10 / 0 / 0 = total 10), pelo que o total é sempre leitura secundária. ⚠ As bandas descritivas de intensidade média — Nula · Ligeira · Moderada · Marcada · Extrema — derivam das ancoragens verbais da própria escala de resposta e NÃO constituem pontos de corte clínicos. ⚠ O instrumento mede INTERFERÊNCIA FUNCIONAL atribuída pelo informante: não mede sintomatologia, gravidade sintomática nem etiologia, e discrepâncias entre sintomas e interferência são informação clínica e não erro de medida. ⚠ As pontuações NÃO são comparáveis entre instrumentos da família EIF, por divergirem as janelas temporais, os referentes e as populações-alvo. ⚠ Sem estudo psicométrico próprio e sem normas portuguesas. ⚠ As referências externas da Forma A provêm de um ensaio clínico em ADULTOS COM PHDA (Coles et al., 2014), com critérios de inclusão que restringiram a variância inicial: a média de referência de 20,5 é elevada e reflete uma amostra selecionada por gravidade, não a população geral. ⚠ A Forma S NÃO dispõe de qualquer referência publicada — não existe versão de informante validada da escala-fonte, nem normas, α, estrutura fatorial ou fidelidade conhecidos —, pelo que não são apresentados valores z nem limiar de mudança fiável e a leitura é exclusivamente por domínio e por comparação intra-sujeito entre momentos. ⚠ Os critérios de remissão (≤6), resposta (≤12) e melhoria (redução ≥4) de Sheehan &amp; Sheehan (2008) são de nível GRUPAL, derivados de médias de ensaios clínicos e não específicos de perturbação: aplicam-se apenas ao total do autorrelato e NÃO substituem o índice de mudança fiável individual, substancialmente mais exigente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIFA-A Total (3 itens, 0–30) — autorrelato sobre trabalho ou estudos, vida social e lazer, e vida familiar | EIFA-S Subescala I — interferência na vida do próprio (2 itens, 0–20), percebida pelo informante | EIFA-S Subescala II — interferência na vida do informante e do agregado (3 itens, 0–30) | EIFA-S Total (5 itens, 0–50) | Sinalização por domínio — assinalável se pontuação SUPERIOR a 5; é o critério primário de leitura e reporta-se domínio a domínio, nunca por agregação | Banda descritiva de intensidade média (média por domínio) — Nula (0) · Ligeira (≤3) · Moderada (≤6) · Marcada (≤9) · Extrema (&gt;9); descreve INTENSIDADE MÉDIA declarada, nunca gravidade clínica nem posição normativa | Dispersão do perfil — perfil dissociado quando a amplitude entre domínios do autorrelato é ≥ 5 pontos, indicando que a leitura pelo total subestimaria o compromisso no domínio mais afetado | Bloco complementar de dias — indicador ecológico externo a QUALQUER total, sem entrar em nenhuma pontuação de escala | Regra de omissão sem imputação — o total de uma escala só é calculado se TODOS os seus itens estiverem respondidos; não há prorrateamento nem estimativa | Distribuição da carga percebida — se a interferência se concentra na vida do próprio, na do informante e agregado, ou se se distribui de forma equilibrada | Convergência entre informantes — comparação entre a média por domínio do autorrelato e a da Subescala I do heterorrelato | Índice de mudança fiável individual (ICF; Jacobson &amp; Truax, 1991) entre M1 e M2 — limiar 6,99 no total do autorrelato; NÃO calculável na Forma S, por ausência de referências | Critérios de nível GRUPAL (Sheehan &amp; Sheehan, 2008), apenas no total do autorrelato — remissão ≤6, resposta ≤12, melhoria com redução ≥4; apresentados em bloco separado do índice individual, que não substituem | Posição face a referências externas (valores z face à média clínica inicial e à pós-tratamento de Coles et al., 2014) — apenas na Forma A, sem conversão percentílica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q_eifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://correiaricardina-ui.github.io/questionarios/EIFA_v1.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIFJ — Escala de Interferência Funcional em Comportamentos de Jogo (Formas J e S)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12–99 anos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mede a INTERFERÊNCIA FUNCIONAL atribuída ao comportamento de jogo em três domínios de vida, na janela do ÚLTIMO MÊS (30 dias) — que DIVERGE dos sete dias da EIFP e da EIFA. Duas formas na mesma aba: EIFJ-J, autorrelato, 3 itens 0–10 (total 0–30), adaptação inspirada (Via B) da SDS-G (Hodgins, 2013; Sheehan, 1983) sem reprodução de conteúdo protegido; e EIFJ-S, heterorrelato do companheiro ou outro significativo, 5 itens 0–10 (total 0–50) em duas subescalas, construção DE RAIZ (Via C). O REFERENTE é selecionado na administração — jogo a dinheiro (CID-11 6C50) ou jogo digital (CID-11 6C51), entidades DISTINTAS — e a FORMULAÇÃO usada («o seu jogo» se não reconhece o comportamento como problema, «o seu problema de jogo» se o reconhece) deve manter-se constante em todos os itens e momentos; ambas ficam registadas. A leitura primária é feita por DOMÍNIO, não pelo total: consideram-se assinalados os domínios com pontuação SUPERIOR a 5 (Williams, 2000), critério que NÃO deve ser confundido com o ponto de corte de Leon et al. (1997), que incide sobre o total e está documentado mas não é aplicado. Um total baixo pode coexistir com interferência extrema num único domínio (ex.: 10 / 0 / 0 = total 10), pelo que o total é sempre leitura secundária. ⚠ As bandas descritivas de intensidade média — Nula · Ligeira · Moderada · Marcada · Extrema — derivam das ancoragens verbais da própria escala de resposta e NÃO constituem pontos de corte clínicos. ⚠ O instrumento mede INTERFERÊNCIA FUNCIONAL atribuída pelo informante: não mede sintomatologia, gravidade sintomática nem etiologia, e discrepâncias entre sintomas e interferência são informação clínica e não erro de medida. ⚠ As pontuações NÃO são comparáveis entre instrumentos da família EIF, por divergirem as janelas temporais, os referentes e as populações-alvo. ⚠ Sem estudo psicométrico próprio e sem normas portuguesas. ⚠ A EIFJ mede interferência funcional, NÃO gravidade sintomática: a gravidade da Perturbação de Jogo no DSM-5-TR estabelece-se por CONTAGEM DE CRITÉRIOS, não por esta escala. ⚠ Em jogo, a MINIMIZAÇÃO e a OCULTAÇÃO são fenómenos clínicos frequentes: uma pontuação baixa no autorrelato NÃO exclui compromisso funcional objetivo e deve ser confrontada com a Forma S e com indicadores financeiros, escolares ou laborais — o painel sinaliza automaticamente as bandas Nula e Ligeira. ⚠ Em MENORES o acesso a jogo a dinheiro é ILEGAL em Portugal: a sua identificação obriga a ponderação de risco e do dever de proteção, independentemente da pontuação obtida, e o painel sinaliza-o automaticamente. ⚠ A Forma S não dispõe de qualquer referência publicada. ⚠ O α inicial reportado por Hodgins é de 0,56, abaixo do aceitável para decisão individual; adota-se α = 0,81 (12 meses), e com o α inicial o limiar de mudança fiável passaria de 9,7 para 14,7 pontos — diferença que deve constar de qualquer relatório que use o índice. ⚠ As médias de referência provêm de uma subamostra de cerca de 42 participantes seguidos nos três momentos, não de normas populacionais</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIFJ-J Total (3 itens, 0–30) — autorrelato sobre trabalho ou estudos, vida social e lazer, e vida familiar, no último mês | EIFJ-S Subescala I — interferência na vida do próprio (2 itens, 0–20), percebida pelo informante | EIFJ-S Subescala II — interferência na vida do informante e do agregado (3 itens, 0–30) | EIFJ-S Total (5 itens, 0–50) | Sinalização por domínio — assinalável se pontuação SUPERIOR a 5; é o critério primário de leitura e reporta-se domínio a domínio, nunca por agregação | Banda descritiva de intensidade média (média por domínio) — Nula (0) · Ligeira (≤3) · Moderada (≤6) · Marcada (≤9) · Extrema (&gt;9); descreve INTENSIDADE MÉDIA declarada, nunca gravidade clínica nem posição normativa | Dispersão do perfil — perfil dissociado quando a amplitude entre domínios do autorrelato é ≥ 5 pontos, indicando que a leitura pelo total subestimaria o compromisso no domínio mais afetado | Bloco complementar de dias — indicador ecológico externo a QUALQUER total, sem entrar em nenhuma pontuação de escala | Regra de omissão sem imputação — o total de uma escala só é calculado se TODOS os seus itens estiverem respondidos; não há prorrateamento nem estimativa | Referente registado — jogo a dinheiro (CID-11 6C50) ou jogo digital (CID-11 6C51); entidades distintas, cuja escolha condiciona a interpretação e consta do relatório | Formulação registada — «o seu jogo» ou «o seu problema de jogo», mantida constante entre momentos e passada automaticamente à terceira pessoa no heterorrelato | Sinalizador de minimização — aviso automático sempre que o autorrelato cai nas bandas Nula ou Ligeira, por a pontuação baixa não ser, neste quadro, informação tranquilizadora | Sinalizador de menor com jogo a dinheiro — aviso automático em vermelho quando a idade é inferior a 18 anos e o referente é jogo a dinheiro, independentemente da pontuação obtida | Índice de mudança fiável individual (ICF; Jacobson &amp; Truax, 1991) entre M1 e M2 — limiar 9,67 no total do autorrelato; NÃO calculável na Forma S, por ausência de referências | Critérios de nível GRUPAL (Sheehan &amp; Sheehan, 2008), apenas no total do autorrelato — remissão ≤6, resposta ≤12, melhoria com redução ≥4; em bloco separado do índice individual | Posição face a referências externas (valores z face à avaliação inicial e ao seguimento aos 12 meses de Hodgins, 2013) — apenas na Forma J, sem conversão percentílica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eifj</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q_eifj</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://correiaricardina-ui.github.io/questionarios/EIFJ_v1.html</t>
   </si>
   <si>
     <t xml:space="preserve">Resumo por Área Clínica (recalcula automaticamente)</t>
@@ -4136,8 +4466,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Catalogo" displayName="Catalogo" ref="A3:M180" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A3:M180"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Catalogo" displayName="Catalogo" ref="A3:M197" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A3:M197"/>
   <tableColumns count="13">
     <tableColumn id="1" name="Nº"/>
     <tableColumn id="2" name="Nome do Instrumento"/>
@@ -4336,7 +4666,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M180"/>
+  <dimension ref="A1:M197"/>
   <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
@@ -6708,10 +7038,10 @@
         <v>131</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>336</v>
+        <v>393</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F58" s="5" t="n">
         <v>5</v>
@@ -6720,22 +7050,22 @@
         <v>99</v>
       </c>
       <c r="H58" s="5" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I58" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="K58" s="6" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M58" s="7" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6744,10 +7074,10 @@
         <v>56</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D59" s="6" t="s">
         <v>17</v>
@@ -6765,19 +7095,19 @@
         <v>5</v>
       </c>
       <c r="I59" s="6" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J59" s="6" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="K59" s="6" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L59" s="6" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M59" s="7" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6786,7 +7116,7 @@
         <v>57</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>122</v>
@@ -6795,7 +7125,7 @@
         <v>17</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F60" s="5" t="n">
         <v>11</v>
@@ -6807,19 +7137,19 @@
         <v>4</v>
       </c>
       <c r="I60" s="6" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="J60" s="6" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="K60" s="6" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L60" s="6" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M60" s="7" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6828,7 +7158,7 @@
         <v>58</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>122</v>
@@ -6837,7 +7167,7 @@
         <v>17</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F61" s="5" t="n">
         <v>10</v>
@@ -6849,19 +7179,19 @@
         <v>6</v>
       </c>
       <c r="I61" s="6" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="J61" s="6" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="K61" s="6" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L61" s="6" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M61" s="7" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6870,7 +7200,7 @@
         <v>59</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>122</v>
@@ -6879,7 +7209,7 @@
         <v>17</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F62" s="5" t="n">
         <v>11</v>
@@ -6891,19 +7221,19 @@
         <v>5</v>
       </c>
       <c r="I62" s="6" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J62" s="6" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="K62" s="6" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="L62" s="6" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M62" s="7" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6912,16 +7242,16 @@
         <v>60</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D63" s="6" t="s">
         <v>272</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F63" s="5" t="n">
         <v>12</v>
@@ -6933,19 +7263,19 @@
         <v>6</v>
       </c>
       <c r="I63" s="6" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J63" s="6" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="K63" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L63" s="6" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M63" s="7" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6954,16 +7284,16 @@
         <v>61</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>272</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F64" s="5" t="n">
         <v>12</v>
@@ -6975,19 +7305,19 @@
         <v>4</v>
       </c>
       <c r="I64" s="6" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="J64" s="6" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="K64" s="6" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="L64" s="6" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M64" s="7" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6996,16 +7326,16 @@
         <v>62</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F65" s="5" t="n">
         <v>0.3</v>
@@ -7017,19 +7347,19 @@
         <v>7</v>
       </c>
       <c r="I65" s="6" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="J65" s="6" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="K65" s="6" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L65" s="6" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M65" s="7" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7038,7 +7368,7 @@
         <v>63</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>210</v>
@@ -7047,7 +7377,7 @@
         <v>33</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F66" s="5" t="n">
         <v>3</v>
@@ -7059,19 +7389,19 @@
         <v>3</v>
       </c>
       <c r="I66" s="6" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="J66" s="6" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="K66" s="6" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L66" s="6" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M66" s="7" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7080,7 +7410,7 @@
         <v>64</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>210</v>
@@ -7089,7 +7419,7 @@
         <v>156</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F67" s="5" t="n">
         <v>3</v>
@@ -7101,19 +7431,19 @@
         <v>3</v>
       </c>
       <c r="I67" s="6" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="J67" s="6" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="K67" s="6" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="L67" s="6" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="M67" s="7" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7122,7 +7452,7 @@
         <v>65</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>210</v>
@@ -7131,7 +7461,7 @@
         <v>17</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="F68" s="5" t="n">
         <v>9</v>
@@ -7143,19 +7473,19 @@
         <v>4</v>
       </c>
       <c r="I68" s="6" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="J68" s="6" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K68" s="6" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L68" s="6" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M68" s="7" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7164,7 +7494,7 @@
         <v>66</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>210</v>
@@ -7173,7 +7503,7 @@
         <v>17</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F69" s="5" t="n">
         <v>10</v>
@@ -7185,19 +7515,19 @@
         <v>2</v>
       </c>
       <c r="I69" s="6" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="J69" s="6" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="K69" s="6" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="L69" s="6" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="M69" s="7" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7206,16 +7536,16 @@
         <v>67</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F70" s="5" t="n">
         <v>1</v>
@@ -7227,19 +7557,19 @@
         <v>7</v>
       </c>
       <c r="I70" s="6" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="J70" s="6" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K70" s="6" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="L70" s="6" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="M70" s="7" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7248,16 +7578,16 @@
         <v>68</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>280</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="F71" s="5" t="n">
         <v>0</v>
@@ -7269,19 +7599,19 @@
         <v>7</v>
       </c>
       <c r="I71" s="6" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="J71" s="6" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="K71" s="6" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L71" s="6" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M71" s="7" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7290,16 +7620,16 @@
         <v>69</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>280</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="F72" s="5" t="n">
         <v>0</v>
@@ -7311,19 +7641,19 @@
         <v>2</v>
       </c>
       <c r="I72" s="6" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="J72" s="6" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="K72" s="6" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L72" s="6" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="M72" s="7" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7332,16 +7662,16 @@
         <v>70</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D73" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F73" s="5" t="n">
         <v>11</v>
@@ -7353,19 +7683,19 @@
         <v>6</v>
       </c>
       <c r="I73" s="6" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="J73" s="6" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="K73" s="6" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L73" s="6" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M73" s="7" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7374,16 +7704,16 @@
         <v>71</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D74" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F74" s="5" t="n">
         <v>7</v>
@@ -7395,19 +7725,19 @@
         <v>6</v>
       </c>
       <c r="I74" s="6" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="J74" s="6" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="K74" s="6" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="L74" s="6" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="M74" s="7" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7416,16 +7746,16 @@
         <v>72</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D75" s="6" t="s">
         <v>33</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F75" s="5" t="n">
         <v>7</v>
@@ -7437,19 +7767,19 @@
         <v>7</v>
       </c>
       <c r="I75" s="6" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="J75" s="6" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="K75" s="6" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="L75" s="6" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M75" s="7" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7458,16 +7788,16 @@
         <v>73</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D76" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F76" s="5" t="n">
         <v>11</v>
@@ -7479,19 +7809,19 @@
         <v>6</v>
       </c>
       <c r="I76" s="6" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="J76" s="6" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="K76" s="6" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="L76" s="6" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="M76" s="7" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7500,16 +7830,16 @@
         <v>74</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D77" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F77" s="5" t="n">
         <v>7</v>
@@ -7521,19 +7851,19 @@
         <v>6</v>
       </c>
       <c r="I77" s="6" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="J77" s="6" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="K77" s="6" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="L77" s="6" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M77" s="7" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7542,16 +7872,16 @@
         <v>75</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D78" s="6" t="s">
         <v>33</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="F78" s="5" t="n">
         <v>2</v>
@@ -7563,19 +7893,19 @@
         <v>6</v>
       </c>
       <c r="I78" s="6" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="J78" s="6" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="K78" s="6" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="L78" s="6" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M78" s="7" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7584,7 +7914,7 @@
         <v>76</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>219</v>
@@ -7605,19 +7935,19 @@
         <v>7</v>
       </c>
       <c r="I79" s="6" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="J79" s="6" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="K79" s="6" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="L79" s="6" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="M79" s="7" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7626,13 +7956,13 @@
         <v>77</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>162</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>265</v>
@@ -7647,19 +7977,19 @@
         <v>4</v>
       </c>
       <c r="I80" s="6" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="J80" s="6" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="K80" s="6" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L80" s="6" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M80" s="7" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7668,10 +7998,10 @@
         <v>78</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D81" s="6" t="s">
         <v>17</v>
@@ -7689,19 +8019,19 @@
         <v>16</v>
       </c>
       <c r="I81" s="6" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="J81" s="6" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="K81" s="6" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L81" s="6" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M81" s="7" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7710,16 +8040,16 @@
         <v>79</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D82" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F82" s="5" t="n">
         <v>8</v>
@@ -7731,19 +8061,19 @@
         <v>16</v>
       </c>
       <c r="I82" s="6" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="J82" s="6" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="K82" s="6" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="L82" s="6" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M82" s="7" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7752,13 +8082,13 @@
         <v>80</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="E83" s="6" t="s">
         <v>95</v>
@@ -7773,19 +8103,19 @@
         <v>16</v>
       </c>
       <c r="I83" s="6" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J83" s="6" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="K83" s="6" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="L83" s="6" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="M83" s="7" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7794,16 +8124,16 @@
         <v>81</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F84" s="5" t="n">
         <v>14</v>
@@ -7815,19 +8145,19 @@
         <v>5</v>
       </c>
       <c r="I84" s="6" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="J84" s="6" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="K84" s="6" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="L84" s="6" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M84" s="7" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7836,16 +8166,16 @@
         <v>82</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="F85" s="5" t="n">
         <v>14</v>
@@ -7857,19 +8187,19 @@
         <v>15</v>
       </c>
       <c r="I85" s="6" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="J85" s="6" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="K85" s="6" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="L85" s="6" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="M85" s="7" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7878,16 +8208,16 @@
         <v>83</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="F86" s="5" t="n">
         <v>12</v>
@@ -7899,19 +8229,19 @@
         <v>8</v>
       </c>
       <c r="I86" s="6" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="J86" s="6" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="K86" s="6" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="L86" s="6" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="M86" s="7" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7920,13 +8250,13 @@
         <v>84</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>210</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="E87" s="6" t="s">
         <v>173</v>
@@ -7941,19 +8271,19 @@
         <v>5</v>
       </c>
       <c r="I87" s="6" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="J87" s="6" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="K87" s="6" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="L87" s="6" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="M87" s="7" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7962,7 +8292,7 @@
         <v>85</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>219</v>
@@ -7971,7 +8301,7 @@
         <v>17</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="F88" s="5" t="n">
         <v>6</v>
@@ -7983,19 +8313,19 @@
         <v>5</v>
       </c>
       <c r="I88" s="6" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="J88" s="6" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="K88" s="6" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="L88" s="6" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="M88" s="7" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8004,16 +8334,16 @@
         <v>86</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="F89" s="5" t="n">
         <v>14</v>
@@ -8025,19 +8355,19 @@
         <v>15</v>
       </c>
       <c r="I89" s="6" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="J89" s="6" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="K89" s="6" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="L89" s="6" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="M89" s="7" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8046,16 +8376,16 @@
         <v>87</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D90" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="F90" s="5" t="n">
         <v>9</v>
@@ -8067,19 +8397,19 @@
         <v>6</v>
       </c>
       <c r="I90" s="6" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="J90" s="6" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="K90" s="6" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="L90" s="6" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="M90" s="7" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8088,7 +8418,7 @@
         <v>88</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C91" s="6" t="s">
         <v>210</v>
@@ -8097,7 +8427,7 @@
         <v>272</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="F91" s="5" t="n">
         <v>13</v>
@@ -8109,19 +8439,19 @@
         <v>6</v>
       </c>
       <c r="I91" s="6" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="J91" s="6" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="K91" s="6" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="L91" s="6" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="M91" s="7" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8130,16 +8460,16 @@
         <v>89</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C92" s="6" t="s">
         <v>210</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="F92" s="5" t="n">
         <v>7</v>
@@ -8151,19 +8481,19 @@
         <v>5</v>
       </c>
       <c r="I92" s="6" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="J92" s="6" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="K92" s="6" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="L92" s="6" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="M92" s="7" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8172,7 +8502,7 @@
         <v>90</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C93" s="6" t="s">
         <v>16</v>
@@ -8181,7 +8511,7 @@
         <v>33</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="F93" s="5" t="n">
         <v>1.5</v>
@@ -8193,19 +8523,19 @@
         <v>2</v>
       </c>
       <c r="I93" s="6" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="J93" s="6" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="K93" s="6" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="L93" s="6" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="M93" s="7" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8214,16 +8544,16 @@
         <v>91</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C94" s="6" t="s">
         <v>16</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="F94" s="5" t="n">
         <v>5</v>
@@ -8235,19 +8565,19 @@
         <v>4</v>
       </c>
       <c r="I94" s="6" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="J94" s="6" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="K94" s="6" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="L94" s="6" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="M94" s="7" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8256,7 +8586,7 @@
         <v>92</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C95" s="6" t="s">
         <v>280</v>
@@ -8265,7 +8595,7 @@
         <v>33</v>
       </c>
       <c r="E95" s="6" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="F95" s="5" t="n">
         <v>0</v>
@@ -8277,19 +8607,19 @@
         <v>3</v>
       </c>
       <c r="I95" s="6" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="J95" s="6" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="K95" s="6" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="L95" s="6" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="M95" s="7" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8298,7 +8628,7 @@
         <v>93</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C96" s="6" t="s">
         <v>280</v>
@@ -8307,7 +8637,7 @@
         <v>33</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="F96" s="5" t="n">
         <v>0</v>
@@ -8319,19 +8649,19 @@
         <v>3</v>
       </c>
       <c r="I96" s="6" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="J96" s="6" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="K96" s="6" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="L96" s="6" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="M96" s="7" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8340,7 +8670,7 @@
         <v>94</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C97" s="6" t="s">
         <v>280</v>
@@ -8361,19 +8691,19 @@
         <v>3</v>
       </c>
       <c r="I97" s="6" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="J97" s="6" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="K97" s="6" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="L97" s="6" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="M97" s="7" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8382,7 +8712,7 @@
         <v>95</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C98" s="6" t="s">
         <v>280</v>
@@ -8403,19 +8733,19 @@
         <v>3</v>
       </c>
       <c r="I98" s="6" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="J98" s="6" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="K98" s="6" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="L98" s="6" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="M98" s="7" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8424,16 +8754,16 @@
         <v>96</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D99" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E99" s="6" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="F99" s="5" t="n">
         <v>17</v>
@@ -8445,19 +8775,19 @@
         <v>3</v>
       </c>
       <c r="I99" s="6" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="J99" s="6" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="K99" s="6" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="L99" s="6" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="M99" s="7" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8466,7 +8796,7 @@
         <v>97</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C100" s="6" t="s">
         <v>186</v>
@@ -8475,7 +8805,7 @@
         <v>17</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="F100" s="5" t="n">
         <v>1.3</v>
@@ -8487,19 +8817,19 @@
         <v>7</v>
       </c>
       <c r="I100" s="6" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="J100" s="6" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="K100" s="6" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="L100" s="6" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="M100" s="7" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8508,16 +8838,16 @@
         <v>98</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C101" s="6" t="s">
         <v>280</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="F101" s="5" t="n">
         <v>3</v>
@@ -8529,19 +8859,19 @@
         <v>6</v>
       </c>
       <c r="I101" s="6" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="J101" s="6" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="K101" s="6" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="L101" s="6" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="M101" s="7" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8550,16 +8880,16 @@
         <v>99</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C102" s="6" t="s">
         <v>280</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="F102" s="5" t="n">
         <v>3</v>
@@ -8571,19 +8901,19 @@
         <v>10</v>
       </c>
       <c r="I102" s="6" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="J102" s="6" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="K102" s="6" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="L102" s="6" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="M102" s="7" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8592,7 +8922,7 @@
         <v>100</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C103" s="6" t="s">
         <v>162</v>
@@ -8601,7 +8931,7 @@
         <v>17</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="F103" s="5" t="n">
         <v>18</v>
@@ -8613,19 +8943,19 @@
         <v>11</v>
       </c>
       <c r="I103" s="6" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="J103" s="6" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="K103" s="6" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="L103" s="6" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="M103" s="7" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8634,16 +8964,16 @@
         <v>101</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D104" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="F104" s="5" t="n">
         <v>17</v>
@@ -8655,19 +8985,19 @@
         <v>5</v>
       </c>
       <c r="I104" s="6" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="J104" s="6" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="K104" s="6" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="L104" s="6" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="M104" s="7" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8676,13 +9006,13 @@
         <v>102</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C105" s="6" t="s">
         <v>219</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="E105" s="6" t="s">
         <v>220</v>
@@ -8697,19 +9027,19 @@
         <v>6</v>
       </c>
       <c r="I105" s="6" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="J105" s="6" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="K105" s="6" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="L105" s="6" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="M105" s="7" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8718,7 +9048,7 @@
         <v>103</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C106" s="6" t="s">
         <v>219</v>
@@ -8727,7 +9057,7 @@
         <v>17</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="F106" s="5" t="n">
         <v>18</v>
@@ -8739,19 +9069,19 @@
         <v>7</v>
       </c>
       <c r="I106" s="6" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="J106" s="6" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="K106" s="6" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="L106" s="6" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="M106" s="7" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8760,16 +9090,16 @@
         <v>104</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D107" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E107" s="6" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="F107" s="5" t="n">
         <v>18</v>
@@ -8781,19 +9111,19 @@
         <v>18</v>
       </c>
       <c r="I107" s="6" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="J107" s="6" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="K107" s="6" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="L107" s="6" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="M107" s="7" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8802,10 +9132,10 @@
         <v>105</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D108" s="6" t="s">
         <v>17</v>
@@ -8823,19 +9153,19 @@
         <v>19</v>
       </c>
       <c r="I108" s="6" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="J108" s="6" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="K108" s="6" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="L108" s="6" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="M108" s="7" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8844,16 +9174,16 @@
         <v>106</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D109" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E109" s="6" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="F109" s="5" t="n">
         <v>10</v>
@@ -8865,19 +9195,19 @@
         <v>10</v>
       </c>
       <c r="I109" s="6" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="J109" s="6" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="K109" s="6" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="L109" s="6" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="M109" s="7" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8886,16 +9216,16 @@
         <v>107</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D110" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="F110" s="5" t="n">
         <v>14</v>
@@ -8907,19 +9237,19 @@
         <v>11</v>
       </c>
       <c r="I110" s="6" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="J110" s="6" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="K110" s="6" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="L110" s="6" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="M110" s="7" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8928,16 +9258,16 @@
         <v>108</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D111" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E111" s="6" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="F111" s="5" t="n">
         <v>10</v>
@@ -8949,19 +9279,19 @@
         <v>10</v>
       </c>
       <c r="I111" s="6" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="J111" s="6" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="K111" s="6" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L111" s="6" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="M111" s="7" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8970,16 +9300,16 @@
         <v>109</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D112" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="F112" s="5" t="n">
         <v>14</v>
@@ -8991,19 +9321,19 @@
         <v>11</v>
       </c>
       <c r="I112" s="6" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="J112" s="6" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="K112" s="6" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="L112" s="6" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="M112" s="7" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9012,10 +9342,10 @@
         <v>110</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D113" s="6" t="s">
         <v>33</v>
@@ -9033,19 +9363,19 @@
         <v>15</v>
       </c>
       <c r="I113" s="6" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="J113" s="6" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="K113" s="6" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="L113" s="6" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="M113" s="7" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9054,10 +9384,10 @@
         <v>111</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D114" s="6" t="s">
         <v>33</v>
@@ -9075,19 +9405,19 @@
         <v>15</v>
       </c>
       <c r="I114" s="6" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="J114" s="6" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="K114" s="6" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="L114" s="6" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="M114" s="7" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9096,10 +9426,10 @@
         <v>112</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D115" s="6" t="s">
         <v>45</v>
@@ -9117,19 +9447,19 @@
         <v>11</v>
       </c>
       <c r="I115" s="6" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="J115" s="6" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="K115" s="6" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="L115" s="6" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="M115" s="7" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9138,10 +9468,10 @@
         <v>113</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D116" s="6" t="s">
         <v>45</v>
@@ -9159,19 +9489,19 @@
         <v>11</v>
       </c>
       <c r="I116" s="6" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="J116" s="6" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="K116" s="6" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="L116" s="6" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="M116" s="7" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9180,16 +9510,16 @@
         <v>114</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C117" s="6" t="s">
         <v>115</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="E117" s="6" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="F117" s="5" t="n">
         <v>12</v>
@@ -9201,19 +9531,19 @@
         <v>8</v>
       </c>
       <c r="I117" s="6" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="J117" s="6" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="K117" s="6" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="L117" s="6" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="M117" s="7" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9222,7 +9552,7 @@
         <v>115</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="C118" s="6" t="s">
         <v>16</v>
@@ -9231,7 +9561,7 @@
         <v>156</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="F118" s="5" t="n">
         <v>3</v>
@@ -9243,19 +9573,19 @@
         <v>13</v>
       </c>
       <c r="I118" s="6" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="J118" s="6" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="K118" s="6" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="L118" s="6" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="M118" s="7" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9264,16 +9594,16 @@
         <v>116</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="C119" s="6" t="s">
         <v>16</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="F119" s="5" t="n">
         <v>3</v>
@@ -9285,19 +9615,19 @@
         <v>13</v>
       </c>
       <c r="I119" s="6" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="J119" s="6" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="K119" s="6" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="L119" s="6" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="M119" s="7" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9306,16 +9636,16 @@
         <v>117</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="F120" s="5" t="n">
         <v>0</v>
@@ -9327,19 +9657,19 @@
         <v>4</v>
       </c>
       <c r="I120" s="6" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="J120" s="6" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="K120" s="6" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="L120" s="6" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="M120" s="7" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9348,7 +9678,7 @@
         <v>118</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C121" s="6" t="s">
         <v>115</v>
@@ -9357,7 +9687,7 @@
         <v>17</v>
       </c>
       <c r="E121" s="6" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="F121" s="5" t="n">
         <v>10</v>
@@ -9369,19 +9699,19 @@
         <v>5</v>
       </c>
       <c r="I121" s="6" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="J121" s="6" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="K121" s="6" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="L121" s="6" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="M121" s="7" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9390,7 +9720,7 @@
         <v>119</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="C122" s="6" t="s">
         <v>115</v>
@@ -9399,7 +9729,7 @@
         <v>17</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="F122" s="5" t="n">
         <v>10</v>
@@ -9411,19 +9741,19 @@
         <v>4</v>
       </c>
       <c r="I122" s="6" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="J122" s="6" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="K122" s="6" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="L122" s="6" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="M122" s="7" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9432,16 +9762,16 @@
         <v>120</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C123" s="6" t="s">
         <v>280</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="E123" s="6" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="F123" s="5" t="n">
         <v>0</v>
@@ -9453,19 +9783,19 @@
         <v>3</v>
       </c>
       <c r="I123" s="6" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="J123" s="6" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="K123" s="6" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="L123" s="6" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="M123" s="7" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9474,16 +9804,16 @@
         <v>121</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="C124" s="6" t="s">
         <v>280</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="F124" s="5" t="n">
         <v>0</v>
@@ -9495,19 +9825,19 @@
         <v>3</v>
       </c>
       <c r="I124" s="6" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="J124" s="6" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="K124" s="6" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="L124" s="6" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="M124" s="7" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9516,16 +9846,16 @@
         <v>122</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D125" s="6" t="s">
         <v>272</v>
       </c>
       <c r="E125" s="6" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="F125" s="5" t="n">
         <v>10</v>
@@ -9537,19 +9867,19 @@
         <v>22</v>
       </c>
       <c r="I125" s="6" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="J125" s="6" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="K125" s="6" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="L125" s="6" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="M125" s="7" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9558,7 +9888,7 @@
         <v>123</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="C126" s="6" t="s">
         <v>280</v>
@@ -9579,19 +9909,19 @@
         <v>3</v>
       </c>
       <c r="I126" s="6" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="J126" s="6" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="K126" s="6" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="L126" s="6" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="M126" s="7" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9600,13 +9930,13 @@
         <v>124</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="C127" s="6" t="s">
         <v>72</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="E127" s="6" t="s">
         <v>95</v>
@@ -9621,19 +9951,19 @@
         <v>9</v>
       </c>
       <c r="I127" s="6" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="J127" s="6" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="K127" s="6" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="L127" s="6" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="M127" s="7" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9642,7 +9972,7 @@
         <v>125</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="C128" s="6" t="s">
         <v>72</v>
@@ -9663,19 +9993,19 @@
         <v>9</v>
       </c>
       <c r="I128" s="6" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="J128" s="6" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="K128" s="6" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="L128" s="6" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="M128" s="7" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9684,7 +10014,7 @@
         <v>126</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="C129" s="6" t="s">
         <v>16</v>
@@ -9705,19 +10035,19 @@
         <v>5</v>
       </c>
       <c r="I129" s="6" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="J129" s="6" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="K129" s="6" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="L129" s="6" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="M129" s="7" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9726,16 +10056,16 @@
         <v>127</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="C130" s="6" t="s">
         <v>16</v>
       </c>
       <c r="D130" s="6" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="F130" s="5" t="n">
         <v>3</v>
@@ -9747,19 +10077,19 @@
         <v>7</v>
       </c>
       <c r="I130" s="6" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="J130" s="6" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="K130" s="6" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="L130" s="6" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="M130" s="7" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9768,16 +10098,16 @@
         <v>128</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C131" s="6" t="s">
         <v>219</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="E131" s="6" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="F131" s="5" t="n">
         <v>9</v>
@@ -9789,19 +10119,19 @@
         <v>8</v>
       </c>
       <c r="I131" s="6" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="J131" s="6" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="K131" s="6" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="L131" s="6" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="M131" s="7" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9810,7 +10140,7 @@
         <v>129</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="C132" s="6" t="s">
         <v>219</v>
@@ -9819,7 +10149,7 @@
         <v>17</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="F132" s="5" t="n">
         <v>9</v>
@@ -9831,19 +10161,19 @@
         <v>8</v>
       </c>
       <c r="I132" s="6" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="J132" s="6" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="K132" s="6" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="L132" s="6" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="M132" s="7" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9852,16 +10182,16 @@
         <v>130</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="C133" s="6" t="s">
         <v>219</v>
       </c>
       <c r="D133" s="6" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="E133" s="6" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="F133" s="5" t="n">
         <v>9</v>
@@ -9873,19 +10203,19 @@
         <v>13</v>
       </c>
       <c r="I133" s="6" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="J133" s="6" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="K133" s="6" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="L133" s="6" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="M133" s="7" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9894,7 +10224,7 @@
         <v>131</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="C134" s="6" t="s">
         <v>219</v>
@@ -9903,7 +10233,7 @@
         <v>17</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="F134" s="5" t="n">
         <v>9</v>
@@ -9915,19 +10245,19 @@
         <v>13</v>
       </c>
       <c r="I134" s="6" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="J134" s="6" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="K134" s="6" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="L134" s="6" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="M134" s="7" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9936,7 +10266,7 @@
         <v>132</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="C135" s="6" t="s">
         <v>219</v>
@@ -9945,7 +10275,7 @@
         <v>17</v>
       </c>
       <c r="E135" s="6" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="F135" s="5" t="n">
         <v>12</v>
@@ -9957,19 +10287,19 @@
         <v>1</v>
       </c>
       <c r="I135" s="6" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="J135" s="6" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="K135" s="6" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="L135" s="6" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="M135" s="7" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9978,7 +10308,7 @@
         <v>133</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="C136" s="6" t="s">
         <v>219</v>
@@ -9999,19 +10329,19 @@
         <v>8</v>
       </c>
       <c r="I136" s="6" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="J136" s="6" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="K136" s="6" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="L136" s="6" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="M136" s="7" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10020,7 +10350,7 @@
         <v>134</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="C137" s="6" t="s">
         <v>219</v>
@@ -10041,19 +10371,19 @@
         <v>8</v>
       </c>
       <c r="I137" s="6" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="J137" s="6" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="K137" s="6" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="L137" s="6" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="M137" s="7" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10062,16 +10392,16 @@
         <v>135</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="F138" s="5" t="n">
         <v>13</v>
@@ -10083,19 +10413,19 @@
         <v>7</v>
       </c>
       <c r="I138" s="6" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="J138" s="6" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="K138" s="6" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="L138" s="6" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="M138" s="7" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10104,16 +10434,16 @@
         <v>136</v>
       </c>
       <c r="B139" s="6" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="C139" s="6" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D139" s="6" t="s">
         <v>272</v>
       </c>
       <c r="E139" s="6" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="F139" s="5" t="n">
         <v>11</v>
@@ -10125,19 +10455,19 @@
         <v>4</v>
       </c>
       <c r="I139" s="6" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="J139" s="6" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="K139" s="6" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="L139" s="6" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="M139" s="7" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10146,16 +10476,16 @@
         <v>137</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="C140" s="6" t="s">
         <v>131</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="F140" s="5" t="n">
         <v>5</v>
@@ -10167,19 +10497,19 @@
         <v>3</v>
       </c>
       <c r="I140" s="6" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="J140" s="6" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="K140" s="6" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="L140" s="6" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="M140" s="7" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10188,13 +10518,13 @@
         <v>138</v>
       </c>
       <c r="B141" s="6" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="C141" s="6" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D141" s="6" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="E141" s="6" t="s">
         <v>95</v>
@@ -10209,19 +10539,19 @@
         <v>6</v>
       </c>
       <c r="I141" s="6" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="J141" s="6" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="K141" s="6" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="L141" s="6" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="M141" s="7" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10230,7 +10560,7 @@
         <v>139</v>
       </c>
       <c r="B142" s="6" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="C142" s="6" t="s">
         <v>219</v>
@@ -10239,7 +10569,7 @@
         <v>33</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="F142" s="5" t="n">
         <v>3</v>
@@ -10251,19 +10581,19 @@
         <v>6</v>
       </c>
       <c r="I142" s="6" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="J142" s="6" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="K142" s="6" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="L142" s="6" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="M142" s="7" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10272,7 +10602,7 @@
         <v>140</v>
       </c>
       <c r="B143" s="6" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="C143" s="6" t="s">
         <v>219</v>
@@ -10281,7 +10611,7 @@
         <v>156</v>
       </c>
       <c r="E143" s="6" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="F143" s="5" t="n">
         <v>3</v>
@@ -10293,19 +10623,19 @@
         <v>6</v>
       </c>
       <c r="I143" s="6" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="J143" s="6" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="K143" s="6" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="L143" s="6" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="M143" s="7" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10314,16 +10644,16 @@
         <v>141</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="C144" s="6" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D144" s="6" t="s">
         <v>172</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="F144" s="5" t="n">
         <v>1.1</v>
@@ -10335,19 +10665,19 @@
         <v>11</v>
       </c>
       <c r="I144" s="6" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="J144" s="6" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="K144" s="6" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="L144" s="6" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="M144" s="7" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10356,16 +10686,16 @@
         <v>142</v>
       </c>
       <c r="B145" s="6" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="C145" s="6" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D145" s="6" t="s">
         <v>172</v>
       </c>
       <c r="E145" s="6" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="F145" s="5" t="n">
         <v>0.7</v>
@@ -10377,19 +10707,19 @@
         <v>9</v>
       </c>
       <c r="I145" s="6" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="J145" s="6" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="K145" s="6" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="L145" s="6" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="M145" s="7" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10398,16 +10728,16 @@
         <v>143</v>
       </c>
       <c r="B146" s="6" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="C146" s="6" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D146" s="6" t="s">
         <v>45</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="F146" s="5" t="n">
         <v>0.7</v>
@@ -10419,19 +10749,19 @@
         <v>6</v>
       </c>
       <c r="I146" s="6" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="J146" s="6" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="K146" s="6" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="L146" s="6" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="M146" s="7" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10440,16 +10770,16 @@
         <v>144</v>
       </c>
       <c r="B147" s="6" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="C147" s="6" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D147" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E147" s="6" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="F147" s="5" t="n">
         <v>1.4</v>
@@ -10461,19 +10791,19 @@
         <v>16</v>
       </c>
       <c r="I147" s="6" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="J147" s="6" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="K147" s="6" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="L147" s="6" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="M147" s="7" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10482,16 +10812,16 @@
         <v>145</v>
       </c>
       <c r="B148" s="6" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="C148" s="6" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D148" s="6" t="s">
         <v>172</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="F148" s="5" t="n">
         <v>0.7</v>
@@ -10503,19 +10833,19 @@
         <v>13</v>
       </c>
       <c r="I148" s="6" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="J148" s="6" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="K148" s="6" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="L148" s="6" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="M148" s="7" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10524,7 +10854,7 @@
         <v>146</v>
       </c>
       <c r="B149" s="6" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="C149" s="6" t="s">
         <v>16</v>
@@ -10545,19 +10875,19 @@
         <v>7</v>
       </c>
       <c r="I149" s="6" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="J149" s="6" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="K149" s="6" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="L149" s="6" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="M149" s="7" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="210" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10566,7 +10896,7 @@
         <v>147</v>
       </c>
       <c r="B150" s="6" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="C150" s="6" t="s">
         <v>16</v>
@@ -10587,19 +10917,19 @@
         <v>7</v>
       </c>
       <c r="I150" s="6" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="J150" s="6" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="K150" s="6" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="L150" s="6" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="M150" s="7" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10608,7 +10938,7 @@
         <v>148</v>
       </c>
       <c r="B151" s="6" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="C151" s="6" t="s">
         <v>219</v>
@@ -10629,19 +10959,19 @@
         <v>4</v>
       </c>
       <c r="I151" s="6" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="J151" s="6" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="K151" s="6" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="L151" s="6" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="M151" s="7" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10650,7 +10980,7 @@
         <v>149</v>
       </c>
       <c r="B152" s="6" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="C152" s="6" t="s">
         <v>72</v>
@@ -10659,7 +10989,7 @@
         <v>17</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="F152" s="5" t="n">
         <v>9</v>
@@ -10671,19 +11001,19 @@
         <v>12</v>
       </c>
       <c r="I152" s="6" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="J152" s="6" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="K152" s="6" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="L152" s="6" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="M152" s="7" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10692,13 +11022,13 @@
         <v>150</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="C153" s="6" t="s">
         <v>131</v>
       </c>
       <c r="D153" s="6" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="E153" s="6" t="s">
         <v>95</v>
@@ -10713,19 +11043,19 @@
         <v>2</v>
       </c>
       <c r="I153" s="6" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="J153" s="6" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="K153" s="6" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="L153" s="6" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="M153" s="7" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10734,7 +11064,7 @@
         <v>151</v>
       </c>
       <c r="B154" s="6" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="C154" s="6" t="s">
         <v>210</v>
@@ -10743,7 +11073,7 @@
         <v>17</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="F154" s="5" t="n">
         <v>16</v>
@@ -10755,19 +11085,19 @@
         <v>4</v>
       </c>
       <c r="I154" s="6" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="J154" s="6" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="K154" s="6" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="L154" s="6" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="M154" s="7" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="220.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10776,16 +11106,16 @@
         <v>152</v>
       </c>
       <c r="B155" s="6" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="C155" s="6" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="D155" s="6" t="s">
         <v>187</v>
       </c>
       <c r="E155" s="6" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="F155" s="5" t="n">
         <v>3</v>
@@ -10797,19 +11127,19 @@
         <v>13</v>
       </c>
       <c r="I155" s="6" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="J155" s="6" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="K155" s="6" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="L155" s="6" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="M155" s="7" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10817,16 +11147,16 @@
         <v>153</v>
       </c>
       <c r="B156" s="6" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="C156" s="6" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="D156" s="6" t="s">
         <v>33</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="F156" s="5" t="n">
         <v>2</v>
@@ -10838,19 +11168,19 @@
         <v>9</v>
       </c>
       <c r="I156" s="6" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="J156" s="6" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="K156" s="6" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="L156" s="6" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="M156" s="7" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10858,16 +11188,16 @@
         <v>154</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="C157" s="6" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="D157" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E157" s="6" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="F157" s="5" t="n">
         <v>7</v>
@@ -10879,19 +11209,19 @@
         <v>8</v>
       </c>
       <c r="I157" s="6" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="J157" s="6" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="K157" s="6" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="L157" s="6" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="M157" s="7" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10899,13 +11229,13 @@
         <v>155</v>
       </c>
       <c r="B158" s="6" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="C158" s="6" t="s">
         <v>16</v>
       </c>
       <c r="D158" s="6" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="E158" s="6" t="s">
         <v>95</v>
@@ -10920,19 +11250,19 @@
         <v>5</v>
       </c>
       <c r="I158" s="6" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="J158" s="6" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="K158" s="6" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="L158" s="6" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="M158" s="7" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10940,10 +11270,10 @@
         <v>156</v>
       </c>
       <c r="B159" s="6" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="C159" s="6" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="D159" s="6" t="s">
         <v>17</v>
@@ -10961,19 +11291,19 @@
         <v>6</v>
       </c>
       <c r="I159" s="6" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="J159" s="6" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="K159" s="6" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="L159" s="6" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="M159" s="7" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10982,10 +11312,10 @@
         <v>157</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="C160" s="6" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="D160" s="6" t="s">
         <v>17</v>
@@ -11003,19 +11333,19 @@
         <v>6</v>
       </c>
       <c r="I160" s="6" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="J160" s="6" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="K160" s="6" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="L160" s="6" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="M160" s="7" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="95.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11024,10 +11354,10 @@
         <v>158</v>
       </c>
       <c r="B161" s="6" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="C161" s="6" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="D161" s="6" t="s">
         <v>33</v>
@@ -11045,19 +11375,19 @@
         <v>6</v>
       </c>
       <c r="I161" s="6" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="J161" s="6" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="K161" s="6" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="L161" s="6" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="M161" s="7" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="95.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11066,16 +11396,16 @@
         <v>159</v>
       </c>
       <c r="B162" s="6" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="C162" s="6" t="s">
         <v>162</v>
       </c>
       <c r="D162" s="6" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="F162" s="5" t="n">
         <v>11</v>
@@ -11087,19 +11417,19 @@
         <v>11</v>
       </c>
       <c r="I162" s="6" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="J162" s="6" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="K162" s="6" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="L162" s="6" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="M162" s="7" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="95.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11108,16 +11438,16 @@
         <v>160</v>
       </c>
       <c r="B163" s="6" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="C163" s="6" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="D163" s="6" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="E163" s="6" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="F163" s="5" t="n">
         <v>6</v>
@@ -11129,19 +11459,19 @@
         <v>4</v>
       </c>
       <c r="I163" s="6" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="J163" s="6" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="K163" s="6" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="L163" s="6" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="M163" s="7" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11150,7 +11480,7 @@
         <v>161</v>
       </c>
       <c r="B164" s="6" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="C164" s="6" t="s">
         <v>219</v>
@@ -11159,7 +11489,7 @@
         <v>17</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="F164" s="5" t="n">
         <v>8</v>
@@ -11171,19 +11501,19 @@
         <v>5</v>
       </c>
       <c r="I164" s="6" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="J164" s="6" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="K164" s="6" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="L164" s="6" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="M164" s="7" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11192,7 +11522,7 @@
         <v>162</v>
       </c>
       <c r="B165" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C165" s="6" t="s">
         <v>219</v>
@@ -11201,7 +11531,7 @@
         <v>33</v>
       </c>
       <c r="E165" s="6" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="F165" s="5" t="n">
         <v>8</v>
@@ -11213,19 +11543,19 @@
         <v>5</v>
       </c>
       <c r="I165" s="6" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="J165" s="6" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="K165" s="6" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="L165" s="6" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="M165" s="7" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11234,16 +11564,16 @@
         <v>163</v>
       </c>
       <c r="B166" s="6" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="C166" s="6" t="s">
         <v>16</v>
       </c>
       <c r="D166" s="6" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F166" s="5" t="n">
         <v>3</v>
@@ -11255,19 +11585,19 @@
         <v>7</v>
       </c>
       <c r="I166" s="6" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="J166" s="6" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="K166" s="6" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="L166" s="6" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="M166" s="7" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11276,10 +11606,10 @@
         <v>164</v>
       </c>
       <c r="B167" s="6" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="C167" s="6" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="D167" s="6" t="s">
         <v>17</v>
@@ -11297,19 +11627,19 @@
         <v>5</v>
       </c>
       <c r="I167" s="6" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="J167" s="6" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="K167" s="6" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="L167" s="6" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="M167" s="7" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11318,7 +11648,7 @@
         <v>165</v>
       </c>
       <c r="B168" s="6" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="C168" s="6" t="s">
         <v>219</v>
@@ -11339,19 +11669,19 @@
         <v>4</v>
       </c>
       <c r="I168" s="6" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="J168" s="6" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="K168" s="6" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="L168" s="6" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="M168" s="7" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11360,7 +11690,7 @@
         <v>166</v>
       </c>
       <c r="B169" s="6" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="C169" s="6" t="s">
         <v>219</v>
@@ -11369,7 +11699,7 @@
         <v>33</v>
       </c>
       <c r="E169" s="6" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="F169" s="5" t="n">
         <v>3</v>
@@ -11381,19 +11711,19 @@
         <v>10</v>
       </c>
       <c r="I169" s="6" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="J169" s="6" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="K169" s="6" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="L169" s="6" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="M169" s="7" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11402,7 +11732,7 @@
         <v>167</v>
       </c>
       <c r="B170" s="6" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="C170" s="6" t="s">
         <v>219</v>
@@ -11411,7 +11741,7 @@
         <v>156</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="F170" s="5" t="n">
         <v>3</v>
@@ -11423,19 +11753,19 @@
         <v>5</v>
       </c>
       <c r="I170" s="6" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="J170" s="6" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="K170" s="6" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="L170" s="6" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="M170" s="7" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11444,16 +11774,16 @@
         <v>168</v>
       </c>
       <c r="B171" s="6" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="C171" s="6" t="s">
         <v>219</v>
       </c>
       <c r="D171" s="6" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="E171" s="6" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F171" s="5" t="n">
         <v>3</v>
@@ -11465,19 +11795,19 @@
         <v>7</v>
       </c>
       <c r="I171" s="6" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="J171" s="6" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="K171" s="6" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="L171" s="6" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="M171" s="7" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11486,7 +11816,7 @@
         <v>169</v>
       </c>
       <c r="B172" s="6" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="C172" s="6" t="s">
         <v>210</v>
@@ -11495,7 +11825,7 @@
         <v>33</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="F172" s="5" t="n">
         <v>3</v>
@@ -11507,19 +11837,19 @@
         <v>18</v>
       </c>
       <c r="I172" s="6" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="J172" s="6" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="K172" s="6" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="L172" s="6" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="M172" s="7" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11528,7 +11858,7 @@
         <v>170</v>
       </c>
       <c r="B173" s="6" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="C173" s="6" t="s">
         <v>280</v>
@@ -11537,7 +11867,7 @@
         <v>17</v>
       </c>
       <c r="E173" s="6" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="F173" s="5" t="n">
         <v>8</v>
@@ -11549,19 +11879,19 @@
         <v>13</v>
       </c>
       <c r="I173" s="6" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="J173" s="6" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="K173" s="6" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="L173" s="6" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="M173" s="7" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11570,7 +11900,7 @@
         <v>171</v>
       </c>
       <c r="B174" s="6" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="C174" s="6" t="s">
         <v>280</v>
@@ -11591,19 +11921,19 @@
         <v>15</v>
       </c>
       <c r="I174" s="6" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="J174" s="6" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="K174" s="6" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="L174" s="6" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="M174" s="7" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11612,10 +11942,10 @@
         <v>172</v>
       </c>
       <c r="B175" s="6" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="C175" s="6" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D175" s="6" t="s">
         <v>17</v>
@@ -11633,19 +11963,19 @@
         <v>11</v>
       </c>
       <c r="I175" s="6" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="J175" s="6" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="K175" s="6" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="L175" s="6" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="M175" s="7" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11654,10 +11984,10 @@
         <v>173</v>
       </c>
       <c r="B176" s="6" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="C176" s="6" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D176" s="6" t="s">
         <v>33</v>
@@ -11675,19 +12005,19 @@
         <v>5</v>
       </c>
       <c r="I176" s="6" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="J176" s="6" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="K176" s="6" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="L176" s="6" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="M176" s="7" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11696,7 +12026,7 @@
         <v>174</v>
       </c>
       <c r="B177" s="6" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="C177" s="6" t="s">
         <v>122</v>
@@ -11705,7 +12035,7 @@
         <v>17</v>
       </c>
       <c r="E177" s="6" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="F177" s="5" t="n">
         <v>8</v>
@@ -11717,19 +12047,19 @@
         <v>9</v>
       </c>
       <c r="I177" s="6" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="J177" s="6" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="K177" s="6" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="L177" s="6" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="M177" s="7" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11738,7 +12068,7 @@
         <v>175</v>
       </c>
       <c r="B178" s="6" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="C178" s="6" t="s">
         <v>122</v>
@@ -11747,7 +12077,7 @@
         <v>33</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="F178" s="5" t="n">
         <v>6</v>
@@ -11759,19 +12089,19 @@
         <v>10</v>
       </c>
       <c r="I178" s="6" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="J178" s="6" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="K178" s="6" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="L178" s="6" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="M178" s="7" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11780,7 +12110,7 @@
         <v>176</v>
       </c>
       <c r="B179" s="6" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="C179" s="6" t="s">
         <v>122</v>
@@ -11789,7 +12119,7 @@
         <v>33</v>
       </c>
       <c r="E179" s="6" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="F179" s="5" t="n">
         <v>3</v>
@@ -11801,19 +12131,19 @@
         <v>22</v>
       </c>
       <c r="I179" s="6" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="J179" s="6" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="K179" s="6" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="L179" s="6" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="M179" s="7" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11822,7 +12152,7 @@
         <v>177</v>
       </c>
       <c r="B180" s="6" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="C180" s="6" t="s">
         <v>122</v>
@@ -11831,7 +12161,7 @@
         <v>33</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="F180" s="5" t="n">
         <v>3</v>
@@ -11843,19 +12173,733 @@
         <v>9</v>
       </c>
       <c r="I180" s="6" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="J180" s="6" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="K180" s="6" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="L180" s="6" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="M180" s="7" t="s">
-        <v>1209</v>
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="181" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A181" s="5" t="n">
+        <f aca="false">ROW()-3</f>
+        <v>178</v>
+      </c>
+      <c r="B181" s="6" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C181" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="D181" s="6" t="s">
+        <v>1212</v>
+      </c>
+      <c r="E181" s="6" t="s">
+        <v>1213</v>
+      </c>
+      <c r="F181" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="G181" s="5" t="n">
+        <v>99</v>
+      </c>
+      <c r="H181" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I181" s="6" t="s">
+        <v>1214</v>
+      </c>
+      <c r="J181" s="6" t="s">
+        <v>1215</v>
+      </c>
+      <c r="K181" s="6" t="s">
+        <v>1216</v>
+      </c>
+      <c r="L181" s="6" t="s">
+        <v>1217</v>
+      </c>
+      <c r="M181" s="7" t="s">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="182" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A182" s="5" t="n">
+        <f aca="false">ROW()-3</f>
+        <v>179</v>
+      </c>
+      <c r="B182" s="6" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C182" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="D182" s="6" t="s">
+        <v>1220</v>
+      </c>
+      <c r="E182" s="6" t="s">
+        <v>1221</v>
+      </c>
+      <c r="F182" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="G182" s="5" t="n">
+        <v>99</v>
+      </c>
+      <c r="H182" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I182" s="6" t="s">
+        <v>1222</v>
+      </c>
+      <c r="J182" s="6" t="s">
+        <v>1223</v>
+      </c>
+      <c r="K182" s="6" t="s">
+        <v>1224</v>
+      </c>
+      <c r="L182" s="6" t="s">
+        <v>1225</v>
+      </c>
+      <c r="M182" s="7" t="s">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="183" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A183" s="5" t="n">
+        <f aca="false">ROW()-3</f>
+        <v>180</v>
+      </c>
+      <c r="B183" s="6" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C183" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="D183" s="6" t="s">
+        <v>1220</v>
+      </c>
+      <c r="E183" s="6" t="s">
+        <v>1221</v>
+      </c>
+      <c r="F183" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="G183" s="5" t="n">
+        <v>99</v>
+      </c>
+      <c r="H183" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I183" s="6" t="s">
+        <v>1228</v>
+      </c>
+      <c r="J183" s="6" t="s">
+        <v>1229</v>
+      </c>
+      <c r="K183" s="6" t="s">
+        <v>1230</v>
+      </c>
+      <c r="L183" s="6" t="s">
+        <v>1231</v>
+      </c>
+      <c r="M183" s="7" t="s">
+        <v>1232</v>
+      </c>
+    </row>
+    <row r="184" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A184" s="5" t="n">
+        <f aca="false">ROW()-3</f>
+        <v>181</v>
+      </c>
+      <c r="B184" s="6" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C184" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="D184" s="6" t="s">
+        <v>1220</v>
+      </c>
+      <c r="E184" s="6" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F184" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="G184" s="5" t="n">
+        <v>99</v>
+      </c>
+      <c r="H184" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="I184" s="6" t="s">
+        <v>1235</v>
+      </c>
+      <c r="J184" s="6" t="s">
+        <v>1236</v>
+      </c>
+      <c r="K184" s="6" t="s">
+        <v>1237</v>
+      </c>
+      <c r="L184" s="6" t="s">
+        <v>1238</v>
+      </c>
+      <c r="M184" s="7" t="s">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="185" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A185" s="5" t="n">
+        <f aca="false">ROW()-3</f>
+        <v>182</v>
+      </c>
+      <c r="B185" s="6" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C185" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="D185" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E185" s="6" t="s">
+        <v>1241</v>
+      </c>
+      <c r="F185" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="G185" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="H185" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="I185" s="6" t="s">
+        <v>1242</v>
+      </c>
+      <c r="J185" s="6" t="s">
+        <v>1243</v>
+      </c>
+      <c r="K185" s="6" t="s">
+        <v>1244</v>
+      </c>
+      <c r="L185" s="6" t="s">
+        <v>1245</v>
+      </c>
+      <c r="M185" s="7" t="s">
+        <v>1246</v>
+      </c>
+    </row>
+    <row r="186" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A186" s="5" t="n">
+        <f aca="false">ROW()-3</f>
+        <v>183</v>
+      </c>
+      <c r="B186" s="6" t="s">
+        <v>1247</v>
+      </c>
+      <c r="C186" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="D186" s="6" t="s">
+        <v>1248</v>
+      </c>
+      <c r="E186" s="6" t="s">
+        <v>1241</v>
+      </c>
+      <c r="F186" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="G186" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="H186" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="I186" s="6" t="s">
+        <v>1249</v>
+      </c>
+      <c r="J186" s="6" t="s">
+        <v>1243</v>
+      </c>
+      <c r="K186" s="6" t="s">
+        <v>1250</v>
+      </c>
+      <c r="L186" s="6" t="s">
+        <v>1251</v>
+      </c>
+      <c r="M186" s="7" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="187" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A187" s="5" t="n">
+        <f aca="false">ROW()-3</f>
+        <v>184</v>
+      </c>
+      <c r="B187" s="6" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C187" s="6" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D187" s="6" t="s">
+        <v>1220</v>
+      </c>
+      <c r="E187" s="6" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F187" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="G187" s="5" t="n">
+        <v>99</v>
+      </c>
+      <c r="H187" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="I187" s="6" t="s">
+        <v>1254</v>
+      </c>
+      <c r="J187" s="6" t="s">
+        <v>1255</v>
+      </c>
+      <c r="K187" s="6" t="s">
+        <v>1256</v>
+      </c>
+      <c r="L187" s="6" t="s">
+        <v>1257</v>
+      </c>
+      <c r="M187" s="7" t="s">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="188" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A188" s="5" t="n">
+        <f aca="false">ROW()-3</f>
+        <v>185</v>
+      </c>
+      <c r="B188" s="6" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C188" s="6" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D188" s="6" t="s">
+        <v>1220</v>
+      </c>
+      <c r="E188" s="6" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F188" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="G188" s="5" t="n">
+        <v>99</v>
+      </c>
+      <c r="H188" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="I188" s="6" t="s">
+        <v>1260</v>
+      </c>
+      <c r="J188" s="6" t="s">
+        <v>1261</v>
+      </c>
+      <c r="K188" s="6" t="s">
+        <v>1262</v>
+      </c>
+      <c r="L188" s="6" t="s">
+        <v>1263</v>
+      </c>
+      <c r="M188" s="7" t="s">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="189" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A189" s="5" t="n">
+        <f aca="false">ROW()-3</f>
+        <v>186</v>
+      </c>
+      <c r="B189" s="6" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C189" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="D189" s="6" t="s">
+        <v>1220</v>
+      </c>
+      <c r="E189" s="6" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F189" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="G189" s="5" t="n">
+        <v>99</v>
+      </c>
+      <c r="H189" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I189" s="6" t="s">
+        <v>1266</v>
+      </c>
+      <c r="J189" s="6" t="s">
+        <v>1267</v>
+      </c>
+      <c r="K189" s="6" t="s">
+        <v>1268</v>
+      </c>
+      <c r="L189" s="6" t="s">
+        <v>1269</v>
+      </c>
+      <c r="M189" s="7" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="190" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A190" s="5" t="n">
+        <f aca="false">ROW()-3</f>
+        <v>187</v>
+      </c>
+      <c r="B190" s="6" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C190" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="D190" s="6" t="s">
+        <v>1212</v>
+      </c>
+      <c r="E190" s="6" t="s">
+        <v>1272</v>
+      </c>
+      <c r="F190" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="G190" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="H190" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I190" s="6" t="s">
+        <v>1266</v>
+      </c>
+      <c r="J190" s="6" t="s">
+        <v>1267</v>
+      </c>
+      <c r="K190" s="6" t="s">
+        <v>1273</v>
+      </c>
+      <c r="L190" s="6" t="s">
+        <v>1274</v>
+      </c>
+      <c r="M190" s="7" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="191" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A191" s="5" t="n">
+        <f aca="false">ROW()-3</f>
+        <v>188</v>
+      </c>
+      <c r="B191" s="6" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C191" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="D191" s="6" t="s">
+        <v>1220</v>
+      </c>
+      <c r="E191" s="6" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F191" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="G191" s="5" t="n">
+        <v>99</v>
+      </c>
+      <c r="H191" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I191" s="6" t="s">
+        <v>1277</v>
+      </c>
+      <c r="J191" s="6" t="s">
+        <v>1278</v>
+      </c>
+      <c r="K191" s="6" t="s">
+        <v>1279</v>
+      </c>
+      <c r="L191" s="6" t="s">
+        <v>1280</v>
+      </c>
+      <c r="M191" s="7" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="192" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A192" s="5" t="n">
+        <f aca="false">ROW()-3</f>
+        <v>189</v>
+      </c>
+      <c r="B192" s="6" t="s">
+        <v>1282</v>
+      </c>
+      <c r="C192" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="D192" s="6" t="s">
+        <v>1212</v>
+      </c>
+      <c r="E192" s="6" t="s">
+        <v>1272</v>
+      </c>
+      <c r="F192" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="G192" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="H192" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I192" s="6" t="s">
+        <v>1277</v>
+      </c>
+      <c r="J192" s="6" t="s">
+        <v>1278</v>
+      </c>
+      <c r="K192" s="6" t="s">
+        <v>1283</v>
+      </c>
+      <c r="L192" s="6" t="s">
+        <v>1284</v>
+      </c>
+      <c r="M192" s="7" t="s">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="193" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A193" s="5" t="n">
+        <f aca="false">ROW()-3</f>
+        <v>190</v>
+      </c>
+      <c r="B193" s="6" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C193" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="D193" s="6" t="s">
+        <v>1212</v>
+      </c>
+      <c r="E193" s="6" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F193" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="G193" s="5" t="n">
+        <v>99</v>
+      </c>
+      <c r="H193" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I193" s="6" t="s">
+        <v>1287</v>
+      </c>
+      <c r="J193" s="6" t="s">
+        <v>1288</v>
+      </c>
+      <c r="K193" s="6" t="s">
+        <v>1289</v>
+      </c>
+      <c r="L193" s="6" t="s">
+        <v>1290</v>
+      </c>
+      <c r="M193" s="7" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="194" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A194" s="5" t="n">
+        <f aca="false">ROW()-3</f>
+        <v>191</v>
+      </c>
+      <c r="B194" s="6" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C194" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="D194" s="6" t="s">
+        <v>1293</v>
+      </c>
+      <c r="E194" s="6" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F194" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="G194" s="5" t="n">
+        <v>99</v>
+      </c>
+      <c r="H194" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I194" s="6" t="s">
+        <v>1294</v>
+      </c>
+      <c r="J194" s="6" t="s">
+        <v>1288</v>
+      </c>
+      <c r="K194" s="6" t="s">
+        <v>1295</v>
+      </c>
+      <c r="L194" s="6" t="s">
+        <v>1296</v>
+      </c>
+      <c r="M194" s="7" t="s">
+        <v>1297</v>
+      </c>
+    </row>
+    <row r="195" customFormat="false" ht="470.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A195" s="5" t="n">
+        <f aca="false">ROW()-3</f>
+        <v>192</v>
+      </c>
+      <c r="B195" s="6" t="s">
+        <v>1298</v>
+      </c>
+      <c r="C195" s="6" t="s">
+        <v>1299</v>
+      </c>
+      <c r="D195" s="6" t="s">
+        <v>1300</v>
+      </c>
+      <c r="E195" s="6" t="s">
+        <v>514</v>
+      </c>
+      <c r="F195" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G195" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="H195" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="I195" s="6" t="s">
+        <v>1301</v>
+      </c>
+      <c r="J195" s="6" t="s">
+        <v>1302</v>
+      </c>
+      <c r="K195" s="6" t="s">
+        <v>1303</v>
+      </c>
+      <c r="L195" s="6" t="s">
+        <v>1304</v>
+      </c>
+      <c r="M195" s="7" t="s">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="196" customFormat="false" ht="481.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A196" s="5" t="n">
+        <f aca="false">ROW()-3</f>
+        <v>193</v>
+      </c>
+      <c r="B196" s="6" t="s">
+        <v>1306</v>
+      </c>
+      <c r="C196" s="6" t="s">
+        <v>1299</v>
+      </c>
+      <c r="D196" s="6" t="s">
+        <v>1307</v>
+      </c>
+      <c r="E196" s="6" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F196" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="G196" s="5" t="n">
+        <v>99</v>
+      </c>
+      <c r="H196" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="I196" s="6" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J196" s="6" t="s">
+        <v>1309</v>
+      </c>
+      <c r="K196" s="6" t="s">
+        <v>1310</v>
+      </c>
+      <c r="L196" s="6" t="s">
+        <v>1311</v>
+      </c>
+      <c r="M196" s="7" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="197" customFormat="false" ht="544" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A197" s="5" t="n">
+        <f aca="false">ROW()-3</f>
+        <v>194</v>
+      </c>
+      <c r="B197" s="6" t="s">
+        <v>1313</v>
+      </c>
+      <c r="C197" s="6" t="s">
+        <v>1299</v>
+      </c>
+      <c r="D197" s="6" t="s">
+        <v>1307</v>
+      </c>
+      <c r="E197" s="6" t="s">
+        <v>1314</v>
+      </c>
+      <c r="F197" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="G197" s="5" t="n">
+        <v>99</v>
+      </c>
+      <c r="H197" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="I197" s="6" t="s">
+        <v>1315</v>
+      </c>
+      <c r="J197" s="6" t="s">
+        <v>1316</v>
+      </c>
+      <c r="K197" s="6" t="s">
+        <v>1317</v>
+      </c>
+      <c r="L197" s="6" t="s">
+        <v>1318</v>
+      </c>
+      <c r="M197" s="7" t="s">
+        <v>1319</v>
       </c>
     </row>
   </sheetData>
@@ -12029,7 +13073,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42"/>
@@ -12039,7 +13083,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>1210</v>
+        <v>1320</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -12049,10 +13093,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1211</v>
+        <v>1321</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>1212</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12064,8 +13108,8 @@
         <v>10</v>
       </c>
       <c r="C3" s="10" t="n">
-        <f aca="false">IF($B$29=0,0,B3/$B$29)</f>
-        <v>0.0564971751412429</v>
+        <f aca="false">IF($B$30=0,0,B3/$B$30)</f>
+        <v>0.0515463917525773</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12077,8 +13121,8 @@
         <v>3</v>
       </c>
       <c r="C4" s="10" t="n">
-        <f aca="false">IF($B$29=0,0,B4/$B$29)</f>
-        <v>0.0169491525423729</v>
+        <f aca="false">IF($B$30=0,0,B4/$B$30)</f>
+        <v>0.0154639175257732</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12087,11 +13131,11 @@
       </c>
       <c r="B5" s="9" t="n">
         <f aca="false">COUNTIF(Catálogo!$C$4:$C$1000,A5)</f>
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="C5" s="10" t="n">
-        <f aca="false">IF($B$29=0,0,B5/$B$29)</f>
-        <v>0.124293785310734</v>
+        <f aca="false">IF($B$30=0,0,B5/$B$30)</f>
+        <v>0.154639175257732</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12100,24 +13144,24 @@
       </c>
       <c r="B6" s="9" t="n">
         <f aca="false">COUNTIF(Catálogo!$C$4:$C$1000,A6)</f>
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C6" s="10" t="n">
-        <f aca="false">IF($B$29=0,0,B6/$B$29)</f>
-        <v>0.0790960451977401</v>
+        <f aca="false">IF($B$30=0,0,B6/$B$30)</f>
+        <v>0.0927835051546392</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B7" s="9" t="n">
         <f aca="false">COUNTIF(Catálogo!$C$4:$C$1000,A7)</f>
         <v>6</v>
       </c>
       <c r="C7" s="10" t="n">
-        <f aca="false">IF($B$29=0,0,B7/$B$29)</f>
-        <v>0.0338983050847458</v>
+        <f aca="false">IF($B$30=0,0,B7/$B$30)</f>
+        <v>0.0309278350515464</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12129,8 +13173,8 @@
         <v>4</v>
       </c>
       <c r="C8" s="10" t="n">
-        <f aca="false">IF($B$29=0,0,B8/$B$29)</f>
-        <v>0.0225988700564972</v>
+        <f aca="false">IF($B$30=0,0,B8/$B$30)</f>
+        <v>0.0206185567010309</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12142,21 +13186,21 @@
         <v>2</v>
       </c>
       <c r="C9" s="10" t="n">
-        <f aca="false">IF($B$29=0,0,B9/$B$29)</f>
-        <v>0.0112994350282486</v>
+        <f aca="false">IF($B$30=0,0,B9/$B$30)</f>
+        <v>0.0103092783505155</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B10" s="9" t="n">
         <f aca="false">COUNTIF(Catálogo!$C$4:$C$1000,A10)</f>
         <v>1</v>
       </c>
       <c r="C10" s="10" t="n">
-        <f aca="false">IF($B$29=0,0,B10/$B$29)</f>
-        <v>0.00564971751412429</v>
+        <f aca="false">IF($B$30=0,0,B10/$B$30)</f>
+        <v>0.00515463917525773</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12168,21 +13212,21 @@
         <v>4</v>
       </c>
       <c r="C11" s="10" t="n">
-        <f aca="false">IF($B$29=0,0,B11/$B$29)</f>
-        <v>0.0225988700564972</v>
+        <f aca="false">IF($B$30=0,0,B11/$B$30)</f>
+        <v>0.0206185567010309</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B12" s="9" t="n">
         <f aca="false">COUNTIF(Catálogo!$C$4:$C$1000,A12)</f>
         <v>12</v>
       </c>
       <c r="C12" s="10" t="n">
-        <f aca="false">IF($B$29=0,0,B12/$B$29)</f>
-        <v>0.0677966101694915</v>
+        <f aca="false">IF($B$30=0,0,B12/$B$30)</f>
+        <v>0.0618556701030928</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12194,8 +13238,8 @@
         <v>9</v>
       </c>
       <c r="C13" s="10" t="n">
-        <f aca="false">IF($B$29=0,0,B13/$B$29)</f>
-        <v>0.0508474576271187</v>
+        <f aca="false">IF($B$30=0,0,B13/$B$30)</f>
+        <v>0.0463917525773196</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12207,217 +13251,238 @@
         <v>18</v>
       </c>
       <c r="C14" s="10" t="n">
-        <f aca="false">IF($B$29=0,0,B14/$B$29)</f>
-        <v>0.101694915254237</v>
+        <f aca="false">IF($B$30=0,0,B14/$B$30)</f>
+        <v>0.0927835051546392</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>520</v>
+        <v>1299</v>
       </c>
       <c r="B15" s="9" t="n">
         <f aca="false">COUNTIF(Catálogo!$C$4:$C$1000,A15)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C15" s="10" t="n">
-        <f aca="false">IF($B$29=0,0,B15/$B$29)</f>
-        <v>0.00564971751412429</v>
+        <f aca="false">IF($B$30=0,0,B15/$B$30)</f>
+        <v>0.0154639175257732</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="B16" s="9" t="n">
         <f aca="false">COUNTIF(Catálogo!$C$4:$C$1000,A16)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C16" s="10" t="n">
-        <f aca="false">IF($B$29=0,0,B16/$B$29)</f>
-        <v>0.0112994350282486</v>
+        <f aca="false">IF($B$30=0,0,B16/$B$30)</f>
+        <v>0.00515463917525773</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>499</v>
+        <v>528</v>
       </c>
       <c r="B17" s="9" t="n">
         <f aca="false">COUNTIF(Catálogo!$C$4:$C$1000,A17)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C17" s="10" t="n">
-        <f aca="false">IF($B$29=0,0,B17/$B$29)</f>
-        <v>0.0169491525423729</v>
+        <f aca="false">IF($B$30=0,0,B17/$B$30)</f>
+        <v>0.0103092783505155</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B18" s="9" t="n">
         <f aca="false">COUNTIF(Catálogo!$C$4:$C$1000,A18)</f>
         <v>1</v>
       </c>
       <c r="C18" s="10" t="n">
-        <f aca="false">IF($B$29=0,0,B18/$B$29)</f>
-        <v>0.00564971751412429</v>
+        <f aca="false">IF($B$30=0,0,B18/$B$30)</f>
+        <v>0.00515463917525773</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
-        <v>379</v>
+        <v>500</v>
       </c>
       <c r="B19" s="9" t="n">
         <f aca="false">COUNTIF(Catálogo!$C$4:$C$1000,A19)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C19" s="10" t="n">
-        <f aca="false">IF($B$29=0,0,B19/$B$29)</f>
-        <v>0.00564971751412429</v>
+        <f aca="false">IF($B$30=0,0,B19/$B$30)</f>
+        <v>0.0154639175257732</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
-        <v>16</v>
+        <v>379</v>
       </c>
       <c r="B20" s="9" t="n">
         <f aca="false">COUNTIF(Catálogo!$C$4:$C$1000,A20)</f>
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C20" s="10" t="n">
-        <f aca="false">IF($B$29=0,0,B20/$B$29)</f>
-        <v>0.0903954802259887</v>
+        <f aca="false">IF($B$30=0,0,B20/$B$30)</f>
+        <v>0.00515463917525773</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>553</v>
+        <v>16</v>
       </c>
       <c r="B21" s="9" t="n">
         <f aca="false">COUNTIF(Catálogo!$C$4:$C$1000,A21)</f>
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C21" s="10" t="n">
-        <f aca="false">IF($B$29=0,0,B21/$B$29)</f>
-        <v>0.0395480225988701</v>
+        <f aca="false">IF($B$30=0,0,B21/$B$30)</f>
+        <v>0.0824742268041237</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>813</v>
+        <v>554</v>
       </c>
       <c r="B22" s="9" t="n">
         <f aca="false">COUNTIF(Catálogo!$C$4:$C$1000,A22)</f>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C22" s="10" t="n">
-        <f aca="false">IF($B$29=0,0,B22/$B$29)</f>
-        <v>0.00564971751412429</v>
+        <f aca="false">IF($B$30=0,0,B22/$B$30)</f>
+        <v>0.0360824742268041</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="9" t="s">
-        <v>427</v>
+        <v>814</v>
       </c>
       <c r="B23" s="9" t="n">
         <f aca="false">COUNTIF(Catálogo!$C$4:$C$1000,A23)</f>
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C23" s="10" t="n">
-        <f aca="false">IF($B$29=0,0,B23/$B$29)</f>
-        <v>0.0508474576271187</v>
+        <f aca="false">IF($B$30=0,0,B23/$B$30)</f>
+        <v>0.00515463917525773</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="s">
-        <v>210</v>
+        <v>428</v>
       </c>
       <c r="B24" s="9" t="n">
         <f aca="false">COUNTIF(Catálogo!$C$4:$C$1000,A24)</f>
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C24" s="10" t="n">
-        <f aca="false">IF($B$29=0,0,B24/$B$29)</f>
-        <v>0.0790960451977401</v>
+        <f aca="false">IF($B$30=0,0,B24/$B$30)</f>
+        <v>0.0463917525773196</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="9" t="s">
-        <v>162</v>
+        <v>210</v>
       </c>
       <c r="B25" s="9" t="n">
         <f aca="false">COUNTIF(Catálogo!$C$4:$C$1000,A25)</f>
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C25" s="10" t="n">
-        <f aca="false">IF($B$29=0,0,B25/$B$29)</f>
-        <v>0.0338983050847458</v>
+        <f aca="false">IF($B$30=0,0,B25/$B$30)</f>
+        <v>0.0721649484536082</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>344</v>
+        <v>162</v>
       </c>
       <c r="B26" s="9" t="n">
         <f aca="false">COUNTIF(Catálogo!$C$4:$C$1000,A26)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C26" s="10" t="n">
-        <f aca="false">IF($B$29=0,0,B26/$B$29)</f>
-        <v>0.0169491525423729</v>
+        <f aca="false">IF($B$30=0,0,B26/$B$30)</f>
+        <v>0.0309278350515464</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
-        <v>1049</v>
+        <v>344</v>
       </c>
       <c r="B27" s="9" t="n">
         <f aca="false">COUNTIF(Catálogo!$C$4:$C$1000,A27)</f>
         <v>3</v>
       </c>
       <c r="C27" s="10" t="n">
-        <f aca="false">IF($B$29=0,0,B27/$B$29)</f>
-        <v>0.0169491525423729</v>
+        <f aca="false">IF($B$30=0,0,B27/$B$30)</f>
+        <v>0.0154639175257732</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="9" t="s">
-        <v>1041</v>
+        <v>1050</v>
       </c>
       <c r="B28" s="9" t="n">
         <f aca="false">COUNTIF(Catálogo!$C$4:$C$1000,A28)</f>
         <v>5</v>
       </c>
       <c r="C28" s="10" t="n">
-        <f aca="false">IF($B$29=0,0,B28/$B$29)</f>
-        <v>0.0282485875706215</v>
+        <f aca="false">IF($B$30=0,0,B28/$B$30)</f>
+        <v>0.0257731958762887</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="11" t="s">
-        <v>1213</v>
-      </c>
-      <c r="B29" s="11" t="n">
+      <c r="A29" s="9" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B29" s="9" t="n">
+        <f aca="false">COUNTIF(Catálogo!$C$4:$C$1000,A29)</f>
+        <v>5</v>
+      </c>
+      <c r="C29" s="10" t="n">
+        <f aca="false">IF($B$30=0,0,B29/$B$30)</f>
+        <v>0.0257731958762887</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="11" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B30" s="11" t="n">
         <f aca="false">COUNTA(Catálogo!$B$4:$B$1000)</f>
-        <v>177</v>
-      </c>
-      <c r="C29" s="12" t="n">
-        <f aca="false">IF(B29=0,0,B29/B29)</f>
+        <v>194</v>
+      </c>
+      <c r="C30" s="12" t="n">
+        <f aca="false">IF(B30=0,0,B30/B30)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>1214</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="14" t="s">
-        <v>1215</v>
+        <v>1324</v>
       </c>
       <c r="B32" s="15" t="str">
         <f aca="false">IF(SUM(B3:B28)=B29,"OK","Existe AREA nova - adicionar linha no resumo")</f>
+        <v>Existe AREA nova - adicionar linha no resumo</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B33" s="1" t="str">
+        <f aca="false">IF(SUM(B3:B29)=B30,"OK","Existe AREA nova - adicionar linha no resumo")</f>
         <v>OK</v>
       </c>
     </row>
@@ -12450,64 +13515,64 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>1216</v>
+        <v>1326</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>1217</v>
+        <v>1327</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1218</v>
+        <v>1328</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>1219</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>1220</v>
+        <v>1330</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>1221</v>
+        <v>1331</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1222</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>1223</v>
+        <v>1333</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>1224</v>
+        <v>1334</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>1225</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>1226</v>
+        <v>1336</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>1227</v>
+        <v>1337</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1228</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>1229</v>
+        <v>1339</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>1230</v>
+        <v>1340</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>1231</v>
+        <v>1341</v>
       </c>
     </row>
   </sheetData>
@@ -12538,56 +13603,56 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>1232</v>
+        <v>1342</v>
       </c>
       <c r="B1" s="8"/>
     </row>
     <row r="2" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="18" t="s">
-        <v>1233</v>
+        <v>1343</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>1234</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="18" t="s">
-        <v>1235</v>
+        <v>1345</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>1236</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="18" t="s">
-        <v>1237</v>
+        <v>1347</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>1238</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
-        <v>1239</v>
+        <v>1349</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>1240</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>1241</v>
+        <v>1351</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>1242</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
-        <v>1243</v>
+        <v>1353</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>1244</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12596,18 +13661,18 @@
     </row>
     <row r="9" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
-        <v>1245</v>
+        <v>1355</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>1246</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="s">
-        <v>1247</v>
+        <v>1357</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>1248</v>
+        <v>1358</v>
       </c>
     </row>
   </sheetData>

--- a/RC_Catalogo_Questionarios_v1.xlsx
+++ b/RC_Catalogo_Questionarios_v1.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1829" uniqueCount="1359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1838" uniqueCount="1365">
   <si>
     <t xml:space="preserve">RC · Catálogo de Questionários — Ricardina Correia · OPP 8233</t>
   </si>
@@ -3493,7 +3493,7 @@
     <t xml:space="preserve">3–7 anos</t>
   </si>
   <si>
-    <t xml:space="preserve">Avalia o temperamento infantil em 15 escalas e 3 dimensões, por hétero-relato do cuidador principal (94 itens, Likert 1–7 com opção NA). Sem normas portuguesas — leitura descritiva e ipsativa, sem valor diagnóstico autónomo.</t>
+    <t xml:space="preserve">Avalia o temperamento infantil em 15 escalas e 3 dimensões, por hétero-relato do cuidador principal (94 itens, Likert 1–7 com opção NA). Sem normas portuguesas — leitura descritiva e ipsativa, sem valor diagnóstico autónomo. ⚠ «Não aplicável» (NA) e omissos são tratados como dados em falta e excluídos do denominador, nunca cotados 0: divergência deliberada face a Lopes (2011), que cotou NA com o valor 0 e assim enviesou sistematicamente as médias para baixo (anomalia A-03 do livro de cotação). Consequência: os resultados obtidos por esta via NÃO são directamente comparáveis com os do estudo português de validação. ⚠ Item 50 — a versão portuguesa lê «Prefere atividades calmas E jogos ativos», quando o original é «prefers quiet activities TO active games»: a conjunção inverte o sentido da afirmação. Item invertido da escala Nível de Atividade, mantido fiel ao protocolo traduzido (sem correcção unilateral, à semelhança das anomalias A-01 a A-05); ponderar esta limitação na leitura isolada do item e da escala.</t>
   </si>
   <si>
     <t xml:space="preserve">Extroversão / Surgência (dimensão, Modelo A: NA + AE + EIP + IM + SG − TI). Afetividade Negativa (IF + DE + ME + TR − SLR). Controlo por Esforço (FA + CI + BIP + SP). Extroversão variante restrita, 4 escalas (Putnam &amp; Rothbart, 2006). Modelo B português (Lopes, 2011), complementar: Extroversão PT, Afetividade Negativa PT, Controlo por Esforço PT. 15 escalas: Nível de Atividade (7 itens); Irritação / Frustração (6); Aproximação / Entusiasmo (6); Foco Atencional (6); Desconforto (6); Sensibilidade / Limiar de Resposta (6); Medo (6); Elevada Intensidade de Prazer (6); Impulsividade (6); Controlo Inibido (6); Baixa Intensidade de Prazer (8); Sensibilidade Percetiva (6); Tristeza (7); Timidez (6); Sorrisos / Gargalhadas (6). Cotação por MÉDIA na métrica 1–7 (ponto neutro = 4); NA e omissos excluídos do denominador. SEM normas portuguesas: bandas descritivas, leitura preferencial por perfil ipsativo intraindividual.</t>
@@ -3983,6 +3983,24 @@
   </si>
   <si>
     <t xml:space="preserve">https://correiaricardina-ui.github.io/questionarios/EIFJ_v1.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRET-RC — Grelha de Resposta ao Erro e à Tarefa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Documenta, por OBSERVAÇÃO ESTRUTURADA do clínico que aplicou a tarefa, o que a criança ou o jovem faz quando a tarefa se torna exigente e quando o erro ocorre. Instrumento CRITERIAL de autoria própria (construção de raiz, Via C), aplicável em qualquer situação estruturada com dificuldade graduada e falha provável — provas cognitivas ou neuropsicológicas, provas de aprendizagem, ou tarefa construída em sessão. Não é específico de instrumento. 30 indicadores organizados em seis dimensões comportamentais, cada um codificado em TRÊS MOMENTOS (início, meio e fim da sessão) numa escala de quatro pontos — 0 não observado · 1 ocorrência isolada · 2 ocorrência repetida · 3 ocorrência pervasiva — mais o código NO (sem oportunidade), que NÃO é equivalente a 0 e constitui a peça central do instrumento: se não houve falha, a dimensão B não pontua zero, fica inobservada; sem esta distinção, uma sessão em que a criança acertou tudo produziria um perfil falsamente tranquilizador. O construto de referência é a resposta autoavaliativa ao fracasso e o padrão de resposta perante a dificuldade (orientação para o domínio da tarefa versus desistência antecipada); as dimensões correspondem, em comportamento observável, às áreas que os instrumentos de autorrelato de perfeccionismo cobrem por via verbal — preocupação com o erro, dúvida sobre a ação e padrões pessoais —, pelo que a GRET-RC se articula diretamente com a CAPS-22 e a CAPS-PR e permite documentar divergências entre o que é referido e o que é feito. Abaixo dos 8–9 anos, idade a partir da qual o autorrelato de perfeccionismo é viável por exigir metacognição sobre padrões pessoais, a via observacional não é solução de recurso: é o método adequado ao construto. ⚠ NÃO é instrumento normativo — sem amostra de aferição, sem normas por idade e SEM PONTUAÇÃO TOTAL: a soma das dimensões implicaria um significado normativo que o instrumento não possui. ⚠ Requer que a situação de observação tenha comportado dificuldade efetiva: sem exigência não há dado. ⚠ Preenchimento pelo clínico durante a sessão ou imediatamente após, nunca por terceiros nem a partir de relato. ⚠ Dimensões com índice de oportunidade inferior a 60% NÃO são reportadas — registam-se como não avaliadas, e a ausência de dado não equivale a ausência de comportamento. ⚠ A secção de FALHA INDUZIDA é opcional e as suas salvaguardas são condição de aplicação, não recomendação: nunca na primeira sessão nem na abertura de uma sessão, não aplicar perante sofrimento marcado, comportamento autolesivo ativo ou desregulação já instalada, duração máxima definida à partida, debriefing obrigatório e imediato, tarefa com sucesso assegurado antes do final e registo obrigatório da indução, do momento e da reação ao debriefing. ⚠ Todas as saídas automáticas são DESCRITIVAS; a interpretação clínica é da exclusiva responsabilidade do psicólogo. ⚠ ESTADO DE INTEGRAÇÃO: aplicação atual em papel (documento Word) com cotação e interpretação em livro Excel dedicado de seis folhas; a versão HTML, a entrada no painel RC e o separador do Apps Script estão POR CONSTRUIR — o syncKey, o ID interno e o link ficam reservados por convenção e a ligação só fica ativa após publicação.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A — Padrão autoimposto (5 indicadores, 15 células de observação): exigência de resultado que a criança impõe a si própria, acima do pedido pela tarefa — refazer elemento já correto, procura de precisão além do exigido, rejeição de solução suficiente, verbalização de padrão de resultado, adiamento da entrega | B — Reação ao erro (4 indicadores de expressão + 1 adaptativo, 12 células): resposta imediata à falha, própria ou assinalada pelo adulto — latência de retoma e interrupção do fluxo, verbalização autoavaliativa negativa, alteração postural, facial ou do contacto ocular, reação desproporcionada ao erro assinalado | C — Antecipação e evitamento (4 + 1, 12 células): comportamento anterior à execução e face à exigência anunciada — verbalização de dificuldade antes de iniciar, latência de início, pedido de saltar, mudar ou terminar, recusa ou abandono antes de tentativa efetiva | D — Procura de validação (5 indicadores, 15 células): dependência do adulto como referência de correção durante a execução — olhar dirigido, pergunta explícita de confirmação, interrupção à espera de resposta, reasseguramento mesmo após desempenho correto, ajuste da resposta pela expressão do adulto e não pela tarefa | E — Sustentação sob carga (3 + 2, 9 células): comportamento perante falhas sucessivas e aumento de dificuldade — repetição da mesma estratégia sem ajuste, escalada de tensão nos itens junto ao limiar da regra de paragem, degradação da qualidade de execução ao longo da sessão | F — Regulação durante a tarefa (5 indicadores, 15 células): tensão motora ou manifestação somática, comportamento autodirigido, alteração do tom ou do volume de voz, necessidade de pausa expressa ou inferida, recuperação prolongada após episódio de desregulação | Itens de resposta adaptativa (+) — B4 deteção autónoma do erro, C5 execução apesar da antecipação negativa, E1 persistência após falhas sucessivas, E2 mudança de estratégia; índice, média e grau próprios; leem-se como qualificadores do perfil e NÃO entram no grau de expressão das dimensões | Índice de oportunidade por dimensão — células codificadas 0–3 sobre itens não (+) × 3 momentos; abaixo de 60% a dimensão é registada como não avaliada, protegendo contra leituras assentes em observação insuficiente | Grau de expressão por dimensão — média dos itens não (+) codificáveis, arredondada a uma casa decimal: Não expresso (0–0,4) · Ligeiro (0,5–1,2) · Moderado (1,3–2,1) · Marcado (2,2–3,0); sem pontuação total, por construção | Evolução entre momentos — Δ entre a média do Fim e a do Início, calculado apenas com pelo menos duas células codificadas em cada momento: Agravamento sob carga (Δ ≥ +0,5) · Estável · Atenuação ao longo da sessão (Δ ≤ −0,5); distingue dificuldade estável de degradação progressiva sob carga acumulada e fadiga | Leitura cruzada resposta adaptativa × expressão — perfil com expressão elevada E itens (+) igualmente elevados descreve quem sustenta a tarefa com custo, leitura clinicamente distinta do perfil elevado sem qualquer resposta adaptativa; assenta em contagem descritiva de dimensões, nunca em soma ou média entre dimensões | Sinalizadores de item — F2 comportamento autodirigido (sinalizado a qualquer ocorrência), C4 recusa ou abandono antes de tentativa efetiva, B2 verbalização autoavaliativa negativa, E5 degradação da execução; reportados ao nível do item por relevância clínica que a média da dimensão dilui | Painel de completude — células codificadas, assinaladas NO e por preencher; célula vazia NÃO é NO, e havendo células por preencher os índices de oportunidade são declarados provisórios | Registo verbatim — até seis verbalizações autoavaliativas registadas literalmente, com o antecedente imediato e o momento da sessão; dado primário e não ilustração, porque a formulação exata (atribuição global e estável versus específica e situacional) tem valor clínico próprio e não é recuperável por paráfrase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gret_rc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q_gret_rc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://correiaricardina-ui.github.io/questionarios/GRET_RC_v1.html</t>
   </si>
   <si>
     <t xml:space="preserve">Resumo por Área Clínica (recalcula automaticamente)</t>
@@ -4466,8 +4484,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Catalogo" displayName="Catalogo" ref="A3:M197" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A3:M197"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Catalogo" displayName="Catalogo" ref="A3:M198" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A3:M198"/>
   <tableColumns count="13">
     <tableColumn id="1" name="Nº"/>
     <tableColumn id="2" name="Nome do Instrumento"/>
@@ -4666,7 +4684,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M197"/>
+  <dimension ref="A1:M198"/>
   <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
@@ -12776,7 +12794,7 @@
         <v>1297</v>
       </c>
     </row>
-    <row r="195" customFormat="false" ht="470.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="195" customFormat="false" ht="470.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="5" t="n">
         <f aca="false">ROW()-3</f>
         <v>192</v>
@@ -12818,7 +12836,7 @@
         <v>1305</v>
       </c>
     </row>
-    <row r="196" customFormat="false" ht="481.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="196" customFormat="false" ht="480.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="5" t="n">
         <f aca="false">ROW()-3</f>
         <v>193</v>
@@ -12860,7 +12878,7 @@
         <v>1312</v>
       </c>
     </row>
-    <row r="197" customFormat="false" ht="544" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="197" customFormat="false" ht="543.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="5" t="n">
         <f aca="false">ROW()-3</f>
         <v>194</v>
@@ -12900,6 +12918,48 @@
       </c>
       <c r="M197" s="7" t="s">
         <v>1319</v>
+      </c>
+    </row>
+    <row r="198" customFormat="false" ht="712.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A198" s="5" t="n">
+        <f aca="false">ROW()-3</f>
+        <v>195</v>
+      </c>
+      <c r="B198" s="6" t="s">
+        <v>1320</v>
+      </c>
+      <c r="C198" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="D198" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="E198" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="F198" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G198" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="H198" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="I198" s="6" t="s">
+        <v>1321</v>
+      </c>
+      <c r="J198" s="6" t="s">
+        <v>1322</v>
+      </c>
+      <c r="K198" s="6" t="s">
+        <v>1323</v>
+      </c>
+      <c r="L198" s="6" t="s">
+        <v>1324</v>
+      </c>
+      <c r="M198" s="7" t="s">
+        <v>1325</v>
       </c>
     </row>
   </sheetData>
@@ -13083,7 +13143,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>1320</v>
+        <v>1326</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -13093,10 +13153,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1321</v>
+        <v>1327</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>1322</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13109,7 +13169,7 @@
       </c>
       <c r="C3" s="10" t="n">
         <f aca="false">IF($B$30=0,0,B3/$B$30)</f>
-        <v>0.0515463917525773</v>
+        <v>0.0512820512820513</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13122,7 +13182,7 @@
       </c>
       <c r="C4" s="10" t="n">
         <f aca="false">IF($B$30=0,0,B4/$B$30)</f>
-        <v>0.0154639175257732</v>
+        <v>0.0153846153846154</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13135,7 +13195,7 @@
       </c>
       <c r="C5" s="10" t="n">
         <f aca="false">IF($B$30=0,0,B5/$B$30)</f>
-        <v>0.154639175257732</v>
+        <v>0.153846153846154</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13148,7 +13208,7 @@
       </c>
       <c r="C6" s="10" t="n">
         <f aca="false">IF($B$30=0,0,B6/$B$30)</f>
-        <v>0.0927835051546392</v>
+        <v>0.0923076923076923</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13161,7 +13221,7 @@
       </c>
       <c r="C7" s="10" t="n">
         <f aca="false">IF($B$30=0,0,B7/$B$30)</f>
-        <v>0.0309278350515464</v>
+        <v>0.0307692307692308</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13174,7 +13234,7 @@
       </c>
       <c r="C8" s="10" t="n">
         <f aca="false">IF($B$30=0,0,B8/$B$30)</f>
-        <v>0.0206185567010309</v>
+        <v>0.0205128205128205</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13187,7 +13247,7 @@
       </c>
       <c r="C9" s="10" t="n">
         <f aca="false">IF($B$30=0,0,B9/$B$30)</f>
-        <v>0.0103092783505155</v>
+        <v>0.0102564102564103</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13200,7 +13260,7 @@
       </c>
       <c r="C10" s="10" t="n">
         <f aca="false">IF($B$30=0,0,B10/$B$30)</f>
-        <v>0.00515463917525773</v>
+        <v>0.00512820512820513</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13213,7 +13273,7 @@
       </c>
       <c r="C11" s="10" t="n">
         <f aca="false">IF($B$30=0,0,B11/$B$30)</f>
-        <v>0.0206185567010309</v>
+        <v>0.0205128205128205</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13226,7 +13286,7 @@
       </c>
       <c r="C12" s="10" t="n">
         <f aca="false">IF($B$30=0,0,B12/$B$30)</f>
-        <v>0.0618556701030928</v>
+        <v>0.0615384615384615</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13239,7 +13299,7 @@
       </c>
       <c r="C13" s="10" t="n">
         <f aca="false">IF($B$30=0,0,B13/$B$30)</f>
-        <v>0.0463917525773196</v>
+        <v>0.0461538461538462</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13252,7 +13312,7 @@
       </c>
       <c r="C14" s="10" t="n">
         <f aca="false">IF($B$30=0,0,B14/$B$30)</f>
-        <v>0.0927835051546392</v>
+        <v>0.0923076923076923</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13265,7 +13325,7 @@
       </c>
       <c r="C15" s="10" t="n">
         <f aca="false">IF($B$30=0,0,B15/$B$30)</f>
-        <v>0.0154639175257732</v>
+        <v>0.0153846153846154</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13278,7 +13338,7 @@
       </c>
       <c r="C16" s="10" t="n">
         <f aca="false">IF($B$30=0,0,B16/$B$30)</f>
-        <v>0.00515463917525773</v>
+        <v>0.00512820512820513</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13291,7 +13351,7 @@
       </c>
       <c r="C17" s="10" t="n">
         <f aca="false">IF($B$30=0,0,B17/$B$30)</f>
-        <v>0.0103092783505155</v>
+        <v>0.0102564102564103</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13304,7 +13364,7 @@
       </c>
       <c r="C18" s="10" t="n">
         <f aca="false">IF($B$30=0,0,B18/$B$30)</f>
-        <v>0.00515463917525773</v>
+        <v>0.00512820512820513</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13317,7 +13377,7 @@
       </c>
       <c r="C19" s="10" t="n">
         <f aca="false">IF($B$30=0,0,B19/$B$30)</f>
-        <v>0.0154639175257732</v>
+        <v>0.0153846153846154</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13330,7 +13390,7 @@
       </c>
       <c r="C20" s="10" t="n">
         <f aca="false">IF($B$30=0,0,B20/$B$30)</f>
-        <v>0.00515463917525773</v>
+        <v>0.00512820512820513</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13343,7 +13403,7 @@
       </c>
       <c r="C21" s="10" t="n">
         <f aca="false">IF($B$30=0,0,B21/$B$30)</f>
-        <v>0.0824742268041237</v>
+        <v>0.0820512820512821</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13356,7 +13416,7 @@
       </c>
       <c r="C22" s="10" t="n">
         <f aca="false">IF($B$30=0,0,B22/$B$30)</f>
-        <v>0.0360824742268041</v>
+        <v>0.0358974358974359</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13369,7 +13429,7 @@
       </c>
       <c r="C23" s="10" t="n">
         <f aca="false">IF($B$30=0,0,B23/$B$30)</f>
-        <v>0.00515463917525773</v>
+        <v>0.00512820512820513</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13378,11 +13438,11 @@
       </c>
       <c r="B24" s="9" t="n">
         <f aca="false">COUNTIF(Catálogo!$C$4:$C$1000,A24)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C24" s="10" t="n">
         <f aca="false">IF($B$30=0,0,B24/$B$30)</f>
-        <v>0.0463917525773196</v>
+        <v>0.0512820512820513</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13395,7 +13455,7 @@
       </c>
       <c r="C25" s="10" t="n">
         <f aca="false">IF($B$30=0,0,B25/$B$30)</f>
-        <v>0.0721649484536082</v>
+        <v>0.0717948717948718</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13408,7 +13468,7 @@
       </c>
       <c r="C26" s="10" t="n">
         <f aca="false">IF($B$30=0,0,B26/$B$30)</f>
-        <v>0.0309278350515464</v>
+        <v>0.0307692307692308</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13421,7 +13481,7 @@
       </c>
       <c r="C27" s="10" t="n">
         <f aca="false">IF($B$30=0,0,B27/$B$30)</f>
-        <v>0.0154639175257732</v>
+        <v>0.0153846153846154</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13434,7 +13494,7 @@
       </c>
       <c r="C28" s="10" t="n">
         <f aca="false">IF($B$30=0,0,B28/$B$30)</f>
-        <v>0.0257731958762887</v>
+        <v>0.0256410256410256</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13447,16 +13507,16 @@
       </c>
       <c r="C29" s="10" t="n">
         <f aca="false">IF($B$30=0,0,B29/$B$30)</f>
-        <v>0.0257731958762887</v>
+        <v>0.0256410256410256</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>1323</v>
+        <v>1329</v>
       </c>
       <c r="B30" s="11" t="n">
         <f aca="false">COUNTA(Catálogo!$B$4:$B$1000)</f>
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C30" s="12" t="n">
         <f aca="false">IF(B30=0,0,B30/B30)</f>
@@ -13465,21 +13525,21 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>1324</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="14" t="s">
-        <v>1324</v>
+        <v>1330</v>
       </c>
       <c r="B32" s="15" t="str">
         <f aca="false">IF(SUM(B3:B28)=B29,"OK","Existe AREA nova - adicionar linha no resumo")</f>
         <v>Existe AREA nova - adicionar linha no resumo</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>1325</v>
+        <v>1331</v>
       </c>
       <c r="B33" s="1" t="str">
         <f aca="false">IF(SUM(B3:B29)=B30,"OK","Existe AREA nova - adicionar linha no resumo")</f>
@@ -13515,64 +13575,64 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>1326</v>
+        <v>1332</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>1327</v>
+        <v>1333</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1328</v>
+        <v>1334</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>1329</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>1330</v>
+        <v>1336</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>1331</v>
+        <v>1337</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1332</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>1333</v>
+        <v>1339</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>1334</v>
+        <v>1340</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>1335</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>1336</v>
+        <v>1342</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>1337</v>
+        <v>1343</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1338</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>1339</v>
+        <v>1345</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>1340</v>
+        <v>1346</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>1341</v>
+        <v>1347</v>
       </c>
     </row>
   </sheetData>
@@ -13603,56 +13663,56 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>1342</v>
+        <v>1348</v>
       </c>
       <c r="B1" s="8"/>
     </row>
     <row r="2" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="18" t="s">
-        <v>1343</v>
+        <v>1349</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>1344</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="18" t="s">
-        <v>1345</v>
+        <v>1351</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>1346</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="18" t="s">
-        <v>1347</v>
+        <v>1353</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>1348</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
-        <v>1349</v>
+        <v>1355</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>1350</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>1351</v>
+        <v>1357</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>1352</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
-        <v>1353</v>
+        <v>1359</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>1354</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13661,18 +13721,18 @@
     </row>
     <row r="9" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
-        <v>1355</v>
+        <v>1361</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>1356</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="s">
-        <v>1357</v>
+        <v>1363</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>1358</v>
+        <v>1364</v>
       </c>
     </row>
   </sheetData>

--- a/RC_Catalogo_Questionarios_v1.xlsx
+++ b/RC_Catalogo_Questionarios_v1.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1838" uniqueCount="1365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1847" uniqueCount="1373">
   <si>
     <t xml:space="preserve">RC · Catálogo de Questionários — Ricardina Correia · OPP 8233</t>
   </si>
@@ -4001,6 +4001,30 @@
   </si>
   <si>
     <t xml:space="preserve">https://correiaricardina-ui.github.io/questionarios/GRET_RC_v1.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AASP — Perfil Sensorial Adolescente e Adulto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Próprio, Criança/Jovem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11–99 anos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caracteriza o PADRÃO DE PROCESSAMENTO SENSORIAL segundo o modelo de Dunn (limiar neurológico × estratégia de autorregulação), através do Adolescent/Adult Sensory Profile (Brown &amp; Dunn, 2002; Pearson/PsychCorp). Autorrelato de 60 itens numa escala 1–5 (1 Quase nunca ≈ 5% das vezes → 5 Quase sempre ≈ 85% ou mais), TODOS no sentido directo — não existe um único item invertido. Cada item pode ainda ser marcado NA quando não houve oportunidade de experimentar a situação. Devolve quatro totais brutos de quadrante (amplitude 15–75 cada) e seis totais de secção sensorial. ⚠ A classificação é DESCRITIVA e não uma medida de gravidade: situa o total de cada quadrante face à distribuição do grupo normativo em cinco posições — −− muito menos · − menos · = semelhante · + mais · ++ muito mais que a maioria das pessoas. Por isso o painel usa PALETA AZUL: verde/laranja/vermelho comunicariam uma gravidade que o instrumento não mede. ⚠ LEITURA CONTRA-INTUITIVA do quadrante Baixo Registo: −− ou − significam MENOS comportamentos de baixo registo, isto é MAIOR detecção de estímulos — não um défice. A direcção clínica de cada quadrante lê-se à luz do modelo de Dunn, nunca por analogia com escalas de sintomas. ⚠ NÃO existem normas portuguesas de validação: os pontos de corte são os do quadro normativo ORIGINAL (amostra norte-americana), aplicados por faixa etária — 11–17, 18–64 e 65 ou mais anos. Abaixo dos 11 anos o instrumento não é aplicável (considerar o Perfil Sensorial 2, versão criança) e a classificação fica suspensa. ⚠ REGRA DE OMISSÕES: 0 NA num quadrante → soma directa; 1 a 2 NA → total prorrateado [(soma dos respondidos ÷ n.º de respondidos) × 15], arredondado à unidade e assinalado como ESTIMATIVA, com a classificação a ser lida com reserva; 3 ou mais NA → quadrante NÃO COTÁVEL, sem classificação. O prorrateamento é uma opção operacional desta plataforma e NÃO consta do manual original. Item por responder é distinto de NA e impede a cotação do quadrante. ⚠ As seis secções sensoriais (A a F) NÃO têm quadro normativo publicado em nenhuma das fontes disponíveis: os seus totais e médias por item servem apenas para localizar, de forma descritiva, os domínios com maior densidade de respostas. ⚠ Instrumento comercial protegido por direitos de autor: a administração deve fazer-se com o protocolo licenciado adoptado pelo serviço. ⚠ Contraparte adolescente/adulta do Perfil Sensorial 2 (PS2), já catalogado — daí a mesma área clínica. ⚠ Cotação validada contra o livro de cotação de referência (0 divergências em 22 casos) e pontos de corte verificados exaustivamente nas 732 combinações faixa × quadrante × total (0 erros).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quadrante 1 — Baixo Registo (15 itens, total 15–75): limiar neurológico alto com estratégia passiva; a pessoa deteta menos estímulos do que a maioria e pode requerer maior intensidade ou saliência para responder | Quadrante 2 — Procura de Sensação (15 itens, 15–75): limiar alto com estratégia activa; a pessoa cria ou procura activamente estimulação sensorial adicional nas suas rotinas | Quadrante 3 — Sensibilidade Sensorial (15 itens, 15–75): limiar baixo com estratégia passiva; a pessoa deteta e reage a estímulos de baixa intensidade que outros filtram, com maior distratibilidade ou desconforto | Quadrante 4 — Evitamento Sensorial (15 itens, 15–75): limiar baixo com estratégia activa; a pessoa restringe ou controla activamente a exposição sensorial | Classificação normativa por quadrante — cinco posições descritivas (−− · − · = · + · ++) face à faixa etária aplicável; posição face à maioria das pessoas, NUNCA medida de gravidade | Faixa normativa aplicada — 11–17, 18–64 ou 65+ anos, determinada automaticamente pela idade; abaixo dos 11 anos a classificação fica suspensa por o instrumento estar fora de âmbito | Estado de cotação por quadrante — Completo · Prorrateado (estimativa, 1 a 2 NA) · Não cotável (3 ou mais NA) · Incompleto (item por responder); é um resultado de validade e condiciona toda a leitura do quadrante | Secção A — Processamento olfativo/gustativo (8 itens): soma e média por item, leitura estritamente descritiva | Secção B — Processamento do movimento (8 itens): soma e média por item, leitura estritamente descritiva | Secção C — Processamento visual (10 itens): soma e média por item, leitura estritamente descritiva | Secção D — Processamento tátil (13 itens): soma e média por item, leitura estritamente descritiva | Secção E — Nível de atividade (10 itens): soma e média por item, leitura estritamente descritiva | Secção F — Processamento auditivo (11 itens): soma e média por item, leitura estritamente descritiva | Distribuição do perfil pelos quatro quadrantes — quantos se afastam do intervalo esperado, em que direcção, e quais se mantêm semelhantes à maioria; é a leitura primária do instrumento | Registo de omissões (NA) — total de itens sem oportunidade de observação, com sinalização automática dos quadrantes prorrateados e dos não cotáveis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aasp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q_aasp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://correiaricardina-ui.github.io/questionarios/AASP_v1.html</t>
   </si>
   <si>
     <t xml:space="preserve">Resumo por Área Clínica (recalcula automaticamente)</t>
@@ -4484,8 +4508,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Catalogo" displayName="Catalogo" ref="A3:M198" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A3:M198"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Catalogo" displayName="Catalogo" ref="A3:M199" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A3:M199"/>
   <tableColumns count="13">
     <tableColumn id="1" name="Nº"/>
     <tableColumn id="2" name="Nome do Instrumento"/>
@@ -4684,7 +4708,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M198"/>
+  <dimension ref="A1:M199"/>
   <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
@@ -12960,6 +12984,48 @@
       </c>
       <c r="M198" s="7" t="s">
         <v>1325</v>
+      </c>
+    </row>
+    <row r="199" customFormat="false" ht="712.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A199" s="5" t="n">
+        <f aca="false">ROW()-3</f>
+        <v>196</v>
+      </c>
+      <c r="B199" s="6" t="s">
+        <v>1326</v>
+      </c>
+      <c r="C199" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D199" s="6" t="s">
+        <v>1327</v>
+      </c>
+      <c r="E199" s="6" t="s">
+        <v>1328</v>
+      </c>
+      <c r="F199" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="G199" s="5" t="n">
+        <v>99</v>
+      </c>
+      <c r="H199" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="I199" s="6" t="s">
+        <v>1329</v>
+      </c>
+      <c r="J199" s="6" t="s">
+        <v>1330</v>
+      </c>
+      <c r="K199" s="6" t="s">
+        <v>1331</v>
+      </c>
+      <c r="L199" s="6" t="s">
+        <v>1332</v>
+      </c>
+      <c r="M199" s="7" t="s">
+        <v>1333</v>
       </c>
     </row>
   </sheetData>
@@ -13143,7 +13209,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>1326</v>
+        <v>1334</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -13153,10 +13219,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1327</v>
+        <v>1335</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>1328</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13169,7 +13235,7 @@
       </c>
       <c r="C3" s="10" t="n">
         <f aca="false">IF($B$30=0,0,B3/$B$30)</f>
-        <v>0.0512820512820513</v>
+        <v>0.0510204081632653</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13182,7 +13248,7 @@
       </c>
       <c r="C4" s="10" t="n">
         <f aca="false">IF($B$30=0,0,B4/$B$30)</f>
-        <v>0.0153846153846154</v>
+        <v>0.0153061224489796</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13195,7 +13261,7 @@
       </c>
       <c r="C5" s="10" t="n">
         <f aca="false">IF($B$30=0,0,B5/$B$30)</f>
-        <v>0.153846153846154</v>
+        <v>0.153061224489796</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13208,7 +13274,7 @@
       </c>
       <c r="C6" s="10" t="n">
         <f aca="false">IF($B$30=0,0,B6/$B$30)</f>
-        <v>0.0923076923076923</v>
+        <v>0.0918367346938776</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13221,7 +13287,7 @@
       </c>
       <c r="C7" s="10" t="n">
         <f aca="false">IF($B$30=0,0,B7/$B$30)</f>
-        <v>0.0307692307692308</v>
+        <v>0.0306122448979592</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13234,7 +13300,7 @@
       </c>
       <c r="C8" s="10" t="n">
         <f aca="false">IF($B$30=0,0,B8/$B$30)</f>
-        <v>0.0205128205128205</v>
+        <v>0.0204081632653061</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13247,7 +13313,7 @@
       </c>
       <c r="C9" s="10" t="n">
         <f aca="false">IF($B$30=0,0,B9/$B$30)</f>
-        <v>0.0102564102564103</v>
+        <v>0.0102040816326531</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13260,7 +13326,7 @@
       </c>
       <c r="C10" s="10" t="n">
         <f aca="false">IF($B$30=0,0,B10/$B$30)</f>
-        <v>0.00512820512820513</v>
+        <v>0.00510204081632653</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13273,7 +13339,7 @@
       </c>
       <c r="C11" s="10" t="n">
         <f aca="false">IF($B$30=0,0,B11/$B$30)</f>
-        <v>0.0205128205128205</v>
+        <v>0.0204081632653061</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13286,7 +13352,7 @@
       </c>
       <c r="C12" s="10" t="n">
         <f aca="false">IF($B$30=0,0,B12/$B$30)</f>
-        <v>0.0615384615384615</v>
+        <v>0.0612244897959184</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13299,7 +13365,7 @@
       </c>
       <c r="C13" s="10" t="n">
         <f aca="false">IF($B$30=0,0,B13/$B$30)</f>
-        <v>0.0461538461538462</v>
+        <v>0.0459183673469388</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13312,7 +13378,7 @@
       </c>
       <c r="C14" s="10" t="n">
         <f aca="false">IF($B$30=0,0,B14/$B$30)</f>
-        <v>0.0923076923076923</v>
+        <v>0.0918367346938776</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13325,7 +13391,7 @@
       </c>
       <c r="C15" s="10" t="n">
         <f aca="false">IF($B$30=0,0,B15/$B$30)</f>
-        <v>0.0153846153846154</v>
+        <v>0.0153061224489796</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13338,7 +13404,7 @@
       </c>
       <c r="C16" s="10" t="n">
         <f aca="false">IF($B$30=0,0,B16/$B$30)</f>
-        <v>0.00512820512820513</v>
+        <v>0.00510204081632653</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13351,7 +13417,7 @@
       </c>
       <c r="C17" s="10" t="n">
         <f aca="false">IF($B$30=0,0,B17/$B$30)</f>
-        <v>0.0102564102564103</v>
+        <v>0.0102040816326531</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13364,7 +13430,7 @@
       </c>
       <c r="C18" s="10" t="n">
         <f aca="false">IF($B$30=0,0,B18/$B$30)</f>
-        <v>0.00512820512820513</v>
+        <v>0.00510204081632653</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13377,7 +13443,7 @@
       </c>
       <c r="C19" s="10" t="n">
         <f aca="false">IF($B$30=0,0,B19/$B$30)</f>
-        <v>0.0153846153846154</v>
+        <v>0.0153061224489796</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13390,7 +13456,7 @@
       </c>
       <c r="C20" s="10" t="n">
         <f aca="false">IF($B$30=0,0,B20/$B$30)</f>
-        <v>0.00512820512820513</v>
+        <v>0.00510204081632653</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13399,11 +13465,11 @@
       </c>
       <c r="B21" s="9" t="n">
         <f aca="false">COUNTIF(Catálogo!$C$4:$C$1000,A21)</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C21" s="10" t="n">
         <f aca="false">IF($B$30=0,0,B21/$B$30)</f>
-        <v>0.0820512820512821</v>
+        <v>0.086734693877551</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13416,7 +13482,7 @@
       </c>
       <c r="C22" s="10" t="n">
         <f aca="false">IF($B$30=0,0,B22/$B$30)</f>
-        <v>0.0358974358974359</v>
+        <v>0.0357142857142857</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13429,7 +13495,7 @@
       </c>
       <c r="C23" s="10" t="n">
         <f aca="false">IF($B$30=0,0,B23/$B$30)</f>
-        <v>0.00512820512820513</v>
+        <v>0.00510204081632653</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13442,7 +13508,7 @@
       </c>
       <c r="C24" s="10" t="n">
         <f aca="false">IF($B$30=0,0,B24/$B$30)</f>
-        <v>0.0512820512820513</v>
+        <v>0.0510204081632653</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13455,7 +13521,7 @@
       </c>
       <c r="C25" s="10" t="n">
         <f aca="false">IF($B$30=0,0,B25/$B$30)</f>
-        <v>0.0717948717948718</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13468,7 +13534,7 @@
       </c>
       <c r="C26" s="10" t="n">
         <f aca="false">IF($B$30=0,0,B26/$B$30)</f>
-        <v>0.0307692307692308</v>
+        <v>0.0306122448979592</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13481,7 +13547,7 @@
       </c>
       <c r="C27" s="10" t="n">
         <f aca="false">IF($B$30=0,0,B27/$B$30)</f>
-        <v>0.0153846153846154</v>
+        <v>0.0153061224489796</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13494,7 +13560,7 @@
       </c>
       <c r="C28" s="10" t="n">
         <f aca="false">IF($B$30=0,0,B28/$B$30)</f>
-        <v>0.0256410256410256</v>
+        <v>0.0255102040816327</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13507,16 +13573,16 @@
       </c>
       <c r="C29" s="10" t="n">
         <f aca="false">IF($B$30=0,0,B29/$B$30)</f>
-        <v>0.0256410256410256</v>
+        <v>0.0255102040816327</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>1329</v>
+        <v>1337</v>
       </c>
       <c r="B30" s="11" t="n">
         <f aca="false">COUNTA(Catálogo!$B$4:$B$1000)</f>
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C30" s="12" t="n">
         <f aca="false">IF(B30=0,0,B30/B30)</f>
@@ -13525,12 +13591,12 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>1330</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="14" t="s">
-        <v>1330</v>
+        <v>1338</v>
       </c>
       <c r="B32" s="15" t="str">
         <f aca="false">IF(SUM(B3:B28)=B29,"OK","Existe AREA nova - adicionar linha no resumo")</f>
@@ -13539,7 +13605,7 @@
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>1331</v>
+        <v>1339</v>
       </c>
       <c r="B33" s="1" t="str">
         <f aca="false">IF(SUM(B3:B29)=B30,"OK","Existe AREA nova - adicionar linha no resumo")</f>
@@ -13575,64 +13641,64 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>1332</v>
+        <v>1340</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>1333</v>
+        <v>1341</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1334</v>
+        <v>1342</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>1335</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>1336</v>
+        <v>1344</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>1337</v>
+        <v>1345</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1338</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>1339</v>
+        <v>1347</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>1340</v>
+        <v>1348</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>1341</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>1342</v>
+        <v>1350</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>1343</v>
+        <v>1351</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1344</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>1345</v>
+        <v>1353</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>1346</v>
+        <v>1354</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>1347</v>
+        <v>1355</v>
       </c>
     </row>
   </sheetData>
@@ -13663,56 +13729,56 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>1348</v>
+        <v>1356</v>
       </c>
       <c r="B1" s="8"/>
     </row>
     <row r="2" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="18" t="s">
-        <v>1349</v>
+        <v>1357</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>1350</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="18" t="s">
-        <v>1351</v>
+        <v>1359</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>1352</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="18" t="s">
-        <v>1353</v>
+        <v>1361</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>1354</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
-        <v>1355</v>
+        <v>1363</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>1356</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>1357</v>
+        <v>1365</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>1358</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
-        <v>1359</v>
+        <v>1367</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>1360</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13721,18 +13787,18 @@
     </row>
     <row r="9" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
-        <v>1361</v>
+        <v>1369</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>1362</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="s">
-        <v>1363</v>
+        <v>1371</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>1364</v>
+        <v>1372</v>
       </c>
     </row>
   </sheetData>
